--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0013.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0013.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong mỏ. Trong Sonoro Sphere đặc biệt này, các hợp kim do Shilang rèn sẽ hỗ trợ bạn một cách bất ngờ.</t>
+          <t>Một vết nứt bí ẩn đột nhiên xuất hiện sâu trong lòng mỏ. Trong Sonoro Sphere đặc biệt này, những hợp kim do Shilang rèn tạo lại mang đến sự trợ giúp bất ngờ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Khe Nứt Nuốt Chửng</t>
+          <t>Vết nứt Nuốt chửng</t>
         </is>
       </c>
     </row>
@@ -707,10 +707,10 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Breath Alloy:
-Concerto Energy của Resonators &lt;color=Wind&gt;Aero&lt;/color&gt; và &lt;color=Light&gt;Spectro&lt;/color&gt; được phục hồi tự động
-Khi Resonators &lt;color=Wind&gt;Aero&lt;/color&gt; sử dụng Intro Skill, một cơn lốc sẽ được triệu hồi.
-Khi Resonators &lt;color=Light&gt;Spectro&lt;/color&gt; sử dụng Intro Skill, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và đánh dấu kẻ địch trong phạm vi nhất định. Một vụ nổ sẽ được kích hoạt khi kẻ địch bị đánh dấu nhận sát thương, gây thêm sát thương.</t>
+          <t>Hợp Kim Hơi Thở:
+Concerto Energy của Resonator &lt;color=Wind&gt;Aero&lt;/color&gt; và &lt;color=Light&gt;Spectro&lt;/color&gt; sẽ tự động hồi phục
+Khi Resonator &lt;color=Wind&gt;Aero&lt;/color&gt; sử dụng Kỹ Năng Khởi Động, một cơn lốc xoáy sẽ được triệu hồi.
+Khi Resonator &lt;color=Light&gt;Spectro&lt;/color&gt; sử dụng Kỹ Năng Khởi Động, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; và đánh dấu kẻ địch trong phạm vi nhất định. Vụ nổ sẽ kích hoạt khi kẻ địch bị đánh dấu nhận DMG, gây thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -778,10 +778,10 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Freezing Alloy:
-Concerto Energy của Resonators &lt;color=Ice&gt;Glacio&lt;/color&gt; và &lt;color=Dark&gt;Havoc&lt;/color&gt; được tự động phục hồi.
-Khi Resonators &lt;color=Ice&gt;Glacio&lt;/color&gt; giải phóng Intro Skill, sẽ đóng băng và đánh dấu tất cả kẻ địch trong phạm vi. Khi kẻ địch bị đánh dấu nhận sát thương, gây thêm &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Khi Resonators &lt;color=Dark&gt;Havoc&lt;/color&gt; giải phóng Intro Skill, sẽ kích hoạt vụ nổ 6 lần xung quanh, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+          <t>Hợp Kim Đông Cứng:
+Năng Lượng Giao Hưởng của Resonator &lt;color=Ice&gt;Glacio&lt;/color&gt; và &lt;color=Dark&gt;Havoc&lt;/color&gt; được tự động phục hồi.
+Khi Resonator &lt;color=Ice&gt;Glacio&lt;/color&gt; sử dụng Kỹ Năng Khởi Động, sẽ đóng băng và đánh dấu tất cả kẻ địch trong phạm vi. Khi kẻ địch bị đánh dấu nhận DMG, gây thêm &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+Khi Resonator &lt;color=Dark&gt;Havoc&lt;/color&gt; sử dụng Kỹ Năng Khởi Động, sẽ kích hoạt vụ nổ 6 lần xung quanh, gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -849,10 +849,10 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hợp Kim Nóng Chảy:
-Resonators &lt;color=Fire&gt;Fusion&lt;/color&gt; và &lt;color=Thunder&gt;Electro&lt;/color&gt; tự động phục hồi Concerto Energy.
-Khi Resonators &lt;color=Fire&gt;Fusion&lt;/color&gt; sử dụng Intro Skill, một cột dung nham sẽ dâng lên dưới chân kẻ địch, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-Khi Resonators &lt;color=Thunder&gt;Electro&lt;/color&gt; sử dụng Intro Skill, 3 tia sét sẽ xuất hiện xung quanh, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Hợp Kim Nóng Rực:
+Năng lượng Concerto của Resonator &lt;color=Fire&gt;Fusion&lt;/color&gt; và &lt;color=Thunder&gt;Electro&lt;/color&gt; sẽ tự động hồi phục.
+Khi Resonator &lt;color=Fire&gt;Fusion&lt;/color&gt; sử dụng Kỹ Năng Giới Thiệu, một cột dung nham sẽ trỗi dậy dưới chân kẻ địch, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.
+Khi Resonator &lt;color=Thunder&gt;Electro&lt;/color&gt; sử dụng Kỹ Năng Giới Thiệu, 3 tia sét sẽ xuất hiện quanh họ, gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -918,8 +918,8 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Rapido Alloy:
-Tốc độ phục hồi &lt;color=highlight&gt;Concerto Energy&lt;/color&gt; của Resonators được tăng lên. Sau khi Resonators sử dụng Intro Skill, &lt;color=highlight&gt;Resonance Energy&lt;/color&gt; sẽ được phục hồi đầy đủ và &lt;color=highlight&gt;Resonance Liberation DMG&lt;/color&gt; sẽ tăng thêm 225%.</t>
+          <t>Hợp Kim Rapido:
+Tốc độ hồi phục &lt;color=highlight&gt;Năng Lượng Hòa Tấu&lt;/color&gt; của Resonator được tăng cường. Sau khi Resonator sử dụng Kỹ Năng Intro, &lt;color=highlight&gt;Resonance Energy&lt;/color&gt; sẽ được hồi đầy và &lt;color=highlight&gt;Sát Thương Resonance Liberation&lt;/color&gt; tăng thêm 225%.</t>
         </is>
       </c>
     </row>
@@ -985,8 +985,8 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Hợp Kim Công Kích:
-Tốc độ phục hồi &lt;color=highlight&gt;Concerto Energy&lt;/color&gt; của Resonators được tăng. Sau khi Resonators sử dụng &lt;color=highlight&gt;Intro Skill&lt;/color&gt;, &lt;color=highlight&gt;Crit. Rate&lt;/color&gt; của họ tăng 100% và &lt;color=highlight&gt;Crit. DMG&lt;/color&gt; tăng 30%. Hiệu ứng tăng Crit. DMG có thể cộng dồn tối đa 15 lần.</t>
+          <t>Hợp Kim Đòn Đánh:
+Tốc độ hồi phục &lt;color=highlight&gt;Concerto Energy&lt;/color&gt; của Resonator được tăng lên. Sau khi Resonator sử dụng &lt;color=highlight&gt;Kỹ Năng Intro&lt;/color&gt;, &lt;color=highlight&gt;Crit. Rate&lt;/color&gt; của họ tăng 100% và &lt;color=highlight&gt;Crit. DMG&lt;/color&gt; tăng 30%. Hiệu ứng tăng Crit. DMG có thể chồng chất lên đến 15 lần.</t>
         </is>
       </c>
     </row>
@@ -1052,8 +1052,8 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Hợp Kim Đe Dọa:
-&lt;color=highlight&gt;Echo Skill DMG&lt;/color&gt; tăng 20% mỗi khi &lt;color=highlight&gt;Echo Skill&lt;/color&gt; được thi triển. Hiệu ứng này có thể cộng dồn tối đa 15 lần. **Cooldown** của &lt;color=highlight&gt;Echo Skill&lt;/color&gt; thi triển trong vòng 8 giây sau &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt; sẽ giảm 100%.</t>
+          <t>Hợp Kim Uy Hiếp:
+&lt;color=highlight&gt;Sát Thương Kỹ Năng Echo&lt;/color&gt; tăng thêm 20% mỗi khi &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt; được kích hoạt. Hiệu ứng này có thể chồng chất lên đến 15 lần. Thời gian hồi chiêu của &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt; được kích hoạt trong vòng 8 giây sau khi sử dụng &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt; sẽ giảm 100%.</t>
         </is>
       </c>
     </row>
@@ -1119,8 +1119,8 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Deafening Alloy:
-&lt;color=highlight&gt;Echo Skill DMG&lt;/color&gt; và &lt;color=highlight&gt;Heavy Attack DMG&lt;/color&gt; tăng 20% khi &lt;color=highlight&gt;Echo Skill&lt;/color&gt; được sử dụng. Hiệu ứng này cộng dồn tối đa 15 lần. &lt;color=highlight&gt;CD của Echo Skill&lt;/color&gt; giảm 50% sau khi Resonators thực hiện &lt;color=highlight&gt;Heavy Attack&lt;/color&gt;.</t>
+          <t>Hợp Kim Đinh Tai:
+&lt;color=highlight&gt;Sát Thương Kỹ Năng Echo&lt;/color&gt; và &lt;color=highlight&gt;Sát Thương Đòn Tấn Công Mạnh&lt;/color&gt; tăng 20% khi &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt; được kích hoạt. Hiệu ứng này có thể chồng chất lên đến 15 lần. &lt;color=highlight&gt;Hồi Chiêu Kỹ Năng Echo&lt;/color&gt; giảm 50% sau khi Resonator thực hiện &lt;color=highlight&gt;Đòn Tấn Công Mạnh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1186,8 +1186,8 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Furious Alloy:
-Cooldown của Echo Skill giảm 50%. &lt;color=highlight&gt;Crit. Rate&lt;/color&gt; và &lt;color=highlight&gt;Crit. DMG&lt;/color&gt; của &lt;color=highlight&gt;Resonance Skill&lt;/color&gt;, &lt;color=highlight&gt;Basic Attack&lt;/color&gt; và &lt;color=highlight&gt;Heavy Attack&lt;/color&gt; tăng lần lượt 100% và 30% sau khi Resonators sử dụng &lt;color=highlight&gt;Echo Skill&lt;/color&gt;. Hiệu ứng tăng Crit. DMG có thể cộng dồn tối đa 15 lần.</t>
+          <t>Hợp Kim Cuồng Nộ:
+Thời gian hồi chiêu Kỹ Năng Tiếng Vọng giảm 50%. Sau khi Resonator sử dụng &lt;color=highlight&gt;Kỹ Năng Tiếng Vọng&lt;/color&gt;, &lt;color=highlight&gt;Crit. Rate&lt;/color&gt; và &lt;color=highlight&gt;Crit. DMG&lt;/color&gt; của &lt;color=highlight&gt;Resonance Skill&lt;/color&gt;, &lt;color=highlight&gt;Đòn Cơ Bản&lt;/color&gt; và &lt;color=highlight&gt;Đòn Nặng&lt;/color&gt; lần lượt tăng 100% và 30%. Hiệu ứng tăng Crit. DMG có thể chồng chất lên đến 15 lần.</t>
         </is>
       </c>
     </row>
@@ -1253,8 +1253,8 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Hợp kim Ethereal:
-Giảm 50% Cooldown của Echo Skill. Sau khi Resonators sử dụng &lt;color=highlight&gt;Echo Skill&lt;/color&gt;, sẽ tạo ra trường gió kéo liên tục kẻ địch vào. Khi trường gió tan, sẽ gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; 1 lần.</t>
+          <t>Hợp Kim Siêu Nhiên:
+Thời gian hồi chiêu Kỹ năng Echo giảm 50%. Sau khi Resonator giải phóng &lt;color=highlight&gt;Kỹ năng Echo&lt;/color&gt;, một trường gió sẽ được tạo ra để liên tục hút kẻ địch vào. Khi trường gió tan biến, &lt;color=Wind&gt;DMG Aero&lt;/color&gt; sẽ được gây ra 1 lần.</t>
         </is>
       </c>
     </row>
@@ -1320,8 +1320,8 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Everlasting Alloy:
-Sử dụng &lt;color=highlight&gt;Intro Skill&lt;/color&gt; giảm &lt;color=highlight&gt;Cooldown Echo Skill&lt;/color&gt; 100% trong 5 giây. &lt;color=highlight&gt;Đánh bại kẻ địch&lt;/color&gt; tăng DMG của Resonators 10%, cộng dồn tối đa 25 lần.</t>
+          <t>Hợp Kim Vĩnh Cửu:
+Kích hoạt &lt;color=highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; sẽ giảm 100% thời gian hồi chiêu của &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt; trong 5 giây. &lt;color=highlight&gt;Đánh bại kẻ địch&lt;/color&gt; tăng Sát Thương cho Resonator thêm 10%, có thể cộng dồn tối đa 25 lần.</t>
         </is>
       </c>
     </row>
@@ -1389,8 +1389,8 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>Hợp Kim Đứt Gãy:
-Sử dụng &lt;color=highlight&gt;Resonance Skill&lt;/color&gt; sẽ giảm Cooldown của Resonance Liberation và phục hồi Resonance Energy.
-Sử dụng &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt; sẽ giảm Cooldown Resonance Skill của tất cả thành viên trong đội, tăng Crit. Rate của Resonance Skill cho họ trong 3 giây và tăng Crit. DMG của Resonance Skill. Hiệu ứng này có thể cộng dồn.</t>
+Khi sử dụng &lt;color=highlight&gt;Resonance Skill&lt;/color&gt;, giảm Thời gian hồi chiêu Resonance Liberation và hồi phục Resonance Energy.
+Khi sử dụng &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt;, giảm Thời gian hồi chiêu Resonance Skill của tất cả thành viên trong đội, tăng Crit. Rate Resonance Skill cho họ trong 3 giây và gia tăng Crit. DMG Resonance Skill. Hiệu ứng này có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -1458,8 +1458,8 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>Hợp Kim Empyrean:
-Khi Resonator đang &lt;color=highlight&gt;ở trên không&lt;/color&gt;, mỗi giây tăng Crit. Rate và Crit. DMG của họ. Mỗi khi Mid-air Attack trúng mục tiêu, sẽ kích hoạt một đòn tấn công bổ sung gây Resonance Liberation DMG.
-Đòn tấn công bổ sung tăng &lt;color=highlight&gt;Resonance Liberation DMG&lt;/color&gt; của Resonator. Hiệu ứng này có thể cộng dồn.</t>
+Khi Resonator đang &lt;color=highlight&gt;ở trên không&lt;/color&gt;, mỗi giây sẽ tăng Crit. Rate và Crit. DMG của họ. Mỗi khi một đòn tấn công trên không trúng mục tiêu, sẽ kích hoạt một đòn tấn công bổ sung gây Sát Thương Resonance Liberation.
+Đòn tấn công bổ sung sẽ gia tăng &lt;color=highlight&gt;Sát Thương Resonance Liberation&lt;/color&gt; của Resonator. Hiệu ứng này có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -1527,10 +1527,10 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Hợp kim Aftersound:
-Increase DMG của Resonators không hoạt động khi &lt;color=highlight&gt;Attack Phối Hợp&lt;/color&gt; trúng mục tiêu. Hiệu ứng này có thể cộng dồn.
-Tất cả thành viên trong đội nhận thêm Resonance Energy và Concerto Energy khi &lt;color=highlight&gt;Attack Phối Hợp&lt;/color&gt; trúng mục tiêu.
-Increase Crit. Rate và Crit. DMG cho tất cả thành viên trong đội trong 8 giây khi &lt;color=highlight&gt;Intro Skill&lt;/color&gt; trúng mục tiêu.</t>
+          <t>Hợp Kim Dư Âm:
+Khi &lt;color=highlight&gt;Tấn Công Phối Hợp&lt;/color&gt; trúng mục tiêu, tăng DMG cho Resonator không hoạt động. Hiệu ứng này có thể chồng chất.
+Khi &lt;color=highlight&gt;Tấn Công Phối Hợp&lt;/color&gt; trúng mục tiêu, tất cả thành viên trong đội nhận thêm Resonance Energy và Năng Lượng Khúc Tấu.
+Khi &lt;color=highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; trúng mục tiêu, tăng Crit. Rate và Crit. DMG cho tất cả thành viên trong đội trong 8 giây.</t>
         </is>
       </c>
     </row>
@@ -1599,9 +1599,9 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>Hợp Kim Nhiệt Huyết:
-Giảm Cooldown &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt;.
-Hạ gục kẻ địch sẽ phục hồi thêm Resonance Energy và Concerto Energy.
-Hạ gục kẻ địch cũng tăng Crit. Rate và Crit. DMG của &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt; cho tất cả thành viên trong đội. Hiệu ứng này có thể cộng dồn.</t>
+Giảm Thời gian hồi chiêu của &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt;.
+Tiêu diệt kẻ địch sẽ phục hồi thêm Resonance Energy và Năng Lượng Giao Hưởng.
+Tiêu diệt kẻ địch cũng tăng Crit. Rate và Crit. DMG của &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt; cho tất cả thành viên trong đội. Hiệu ứng này có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -1668,9 +1668,9 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Crescent Alloy:
-Giảm Cooldown của &lt;color=highlight&gt;Echo Skill&lt;/color&gt;. Khi bắt đầu và kết thúc &lt;color=highlight&gt;Echo Skill&lt;/color&gt;, tung một Crescent Slash bên cạnh Echo đang hoạt động, gây Echo Skill DMG lên kẻ địch.
-Đánh bại kẻ địch sẽ tăng ATK DMG và Echo Skill DMG cho tất cả thành viên trong đội.</t>
+          <t>Hợp Kim Lưỡi Liềm:
+Giảm Thời gian hồi chiêu &lt;color=highlight&gt;Kỹ Năng Tiếng Vọng&lt;/color&gt;. Khi bắt đầu và kết thúc &lt;color=highlight&gt;Kỹ Năng Tiếng Vọng&lt;/color&gt;, tạo một Lưỡi Kiếm Lưỡi Liềm bên cạnh Tiếng Vọng đang kích hoạt, gây Sát Thương Kỹ Năng Tiếng Vọng lên kẻ địch.
+Tiêu diệt kẻ địch sẽ tăng Sát Thương Tấn Công và Sát Thương Kỹ Năng Tiếng Vọng cho tất cả thành viên trong đội.</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>Hợp Kim Trì Trệ:
-Giảm Cooldown của &lt;color=highlight&gt;Echo Skill&lt;/color&gt;. &lt;color=highlight&gt;Echo Skill&lt;/color&gt; gây hiệu ứng Trì Trệ lên kẻ địch và đánh dấu chúng. Mỗi kẻ địch bị đánh dấu sẽ chịu thêm DMG.</t>
+Giảm Thời gian hồi chiêu &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt;. &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt; gây hiệu ứng Trì Trệ và đánh dấu kẻ địch. Mỗi kẻ địch bị đánh dấu sẽ chịu thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -1805,8 +1805,8 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>Hợp Kim Nuốt Chửng:
-Increase Crit. Rate và Crit. DMG của Resonance Skill trong một khoảng thời gian nhất định sau khi sử dụng &lt;color=highlight&gt;Echo Skill&lt;/color&gt;. Hiệu ứng này có thể cộng dồn.
-Đánh bại kẻ địch bằng &lt;color=highlight&gt;Resonance Skill&lt;/color&gt; sẽ giảm Cooldown của Echo Skill và Resonance Skill của Resonator và phục hồi một lượng Concerto Energy nhất định.</t>
+Tăng Crit. Rate và Crit. DMG của Resonance Skill trong một khoảng thời gian sau khi sử dụng &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt;. Hiệu ứng này có thể chồng chất.
+Tiêu diệt kẻ địch bằng &lt;color=highlight&gt;Resonance Skill&lt;/color&gt; sẽ giảm Thời gian hồi chiêu của Kỹ Năng Echo và Resonance Skill của Resonator, đồng thời phục hồi một lượng Concerto Energy nhất định.</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>TD-副本测试2</t>
+          <t>Kiểm tra phụ bản TD 2</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>TD-Bản Thử Nghiệm 3</t>
+          <t>Kiểm tra phụ bản TD 3</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Những bức ảnh à? Nếu có thể, tôi cũng muốn "xem" chúng... Chỉ là trò đùa thôi.</t>
+          <t>Chụp ảnh á? Tao muốn "tận mắt" nhìn chúng hơn... Chỉ là đùa thôi.</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Chụp thoải mái đi. Tôi đã xác nhận là sẽ được trả tiền làm thêm rồi.</t>
+          <t>Chụp đi chụp đi. Tôi đã xác nhận là sẽ được trả tiền làm thêm mà.</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Lửa Night Black Alley</t>
+          <t>Ngọn Lửa Đêm Ở Ngõ Đen</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Ánh nắng lấp lánh trên tuyết, tỏa ra hơi ấm của mùa xuân.</t>
+          <t>Ánh dương lấp lánh trên tuyết, tỏa ra hơi ấm của mùa xuân.</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Giờ Phút Hy Vọng</t>
+          <t>Giờ Khắc Hy Vọng</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Tư thế đẹp cũng chẳng ích gì trong săn bắn, nhưng nếu cậu nhất quyết...</t>
+          <t>Tư thế đẹp đẽ chẳng giúp ích gì trong cuộc săn đâu, nhưng nếu cậu muốn...</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Tái Sinh Từ Vực Thẳm</t>
+          <t>Tái Sinh Từ Vực Sâu</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Hình dung các động tác trong chiến đấu để làm tài liệu tham khảo cải thiện sau này... Một cách tiếp cận thú vị.</t>
+          <t>Ghi lại chuyển động trong chiến đấu để làm tư liệu cải tiến sau này... Một cách tiếp cận thú vị.</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Dance Qingloong</t>
+          <t>Vũ Điệu Thanh Long</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Cuối cùng cũng có người đến xem buổi biểu diễn của ta đúng giờ.</t>
+          <t>Cuối cùng cũng có người đến đúng lúc cho buổi trình diễn của ta rồi.</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Ảo Ảnh Viễn Xứ</t>
+          <t>Bóng Ma Viễn Xứ</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Làm sao để nhìn qua ống kính của bạn?</t>
+          <t>Làm thế nào để nhìn qua ống kính của cậu?</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Càng huy hoàng. Càng thanh nhã!</t>
+          <t>Càng huy hoàng hơn! Càng thanh tao hơn!</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Vầng Trăng Sáng Trong Bóng Tối</t>
+          <t>Vầng Trăng Trong Bóng Tối</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Thanh kiếm có thể cảm nhận được hình dạng của chính nó.</t>
+          <t>Kiếm có thể cảm nhận được hình dạng của chính nó.</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Chiêu đó khó thực hiện quá... Có lẽ tôi phải đòi tăng lương làm thêm giờ mới được.</t>
+          <t>Chiêu đó khó thực hiện thật đấy... Chắc phải đòi thêm tiền làm ngoài giờ mới được.</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Lửa Night Black Alley</t>
+          <t>Ngọn Lửa Đêm Ở Ngõ Đen</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Dưới ánh sáng trong trẻo này, tuyết sẽ tan đi, để chúng ta cùng ngắm nhìn muôn ngàn núi non.</t>
+          <t>Ước gì tuyết được quét sạch dưới ánh sáng trong veo này, để ta cùng ngắm nhìn muôn trùng núi non.</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Giờ Phút Hy Vọng</t>
+          <t>Giờ Khắc Hy Vọng</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Quan sát đi. Đây mới là tư thế săn bắn thực thụ.</t>
+          <t>Quan sát đi. Đây mới là tư thế săn mồi thực thụ.</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Tái Sinh Từ Vực Thẳm</t>
+          <t>Tái Sinh Từ Vực Sâu</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Những bản ghi hình phù hợp quả thực rất hữu ích trong việc nâng cao kỹ năng chiến đấu. Cảm ơn bạn rất nhiều, người bạn của tôi.</t>
+          <t>Những bản ghi hình phù hợp quả thật rất hữu ích cho việc nâng cao kỹ năng chiến đấu. Cảm ơn cậu nhiều nhé, bạn tôi.</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Dance Qingloong</t>
+          <t>Vũ Điệu Thanh Long</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Ta sẽ không tiết lộ thêm điều gì với kẻ địch.</t>
+          <t>Ta sẽ không tiết lộ thêm điều gì cho kẻ thù của mình.</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Ảo Ảnh Viễn Xứ</t>
+          <t>Bóng Ma Viễn Xứ</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Hehe, tôi biết cậu sẽ không làm tôi thất vọng mà!</t>
+          <t>Hehe, mình biết cậu sẽ không làm mình thất vọng mà!</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Hãy cùng chụp lấy vầng trăng!</t>
+          <t>Lại đây, cùng ta bắt trăng nào!</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Vầng Trăng Sáng Trong Bóng Tối</t>
+          <t>Vầng Trăng Trong Bóng Tối</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Chụp ảnh Qiuyuan thực hiện Heavy Attack</t>
+          <t>Ảnh Qiuyuan thực hiện Tấn Công mạnh</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Chụp ảnh Qiuyuan thực hiện Đòn Lao Dốc</t>
+          <t>Ảnh Qiuyuan thực hiện Tấn Công bổ nhào</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Chụp ảnh Qiuyuan viết (Bộ lọc: Noir)</t>
+          <t>Ảnh Qiuyuan đang viết (Bộ lọc: Noir)</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Chụp ảnh Zani thực hiện Basic Attack Giai đoạn 3</t>
+          <t>Ảnh Zani thực hiện Tấn Công cơ bản Giai đoạn 3</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Chụp ảnh Zani thực hiện Heavy Attack</t>
+          <t>Ảnh Zani thực hiện Đòn Tấn Công Mạnh</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Chụp ảnh Zani thực hiện Plunging Attack</t>
+          <t>Ảnh Zani thực hiện Đòn Lao Xuống</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jinhsi thực hiện Basic Attack Stage 4</t>
+          <t>Ảnh Jinhsi thực hiện Basic Attack Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jinhsi thực hiện Basic Attack Stage 4 của Incarnation</t>
+          <t>Ảnh Jinhsi thực hiện Basic Attack Hóa Thân Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jinhsi thực hiện Heavy Attack</t>
+          <t>Ảnh Jinhsi thực hiện Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Chụp ảnh Galbrena thực hiện Basic Attack Stage 2</t>
+          <t>Hình ảnh Galbrena thực hiện Basic Attack Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Chụp ảnh Galbrena thực hiện Basic Attack Stage 4</t>
+          <t>Hình ảnh Galbrena thực hiện Basic Attack Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Chụp ảnh Galbrena thực hiện Heavy Attack</t>
+          <t>Hình ảnh Galbrena thực hiện Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jiyan thực hiện Resonance Skill</t>
+          <t>Ảnh Jiyan thực hiện Resonance Skill</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Hình ảnh Jiyan thực hiện Basic Attack Stage 5</t>
+          <t>Ảnh Jiyan thực hiện Basic Attack Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jiyan thực hiện Plunging Attack</t>
+          <t>Ảnh Jiyan thực hiện Tấn Công Lao Xuống</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Chụp ảnh Phrolova thực hiện Basic Attack Stage 2</t>
+          <t>Ảnh Phrolova thực hiện Giai Đoạn 2 của Basic Attack</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Chụp ảnh Phrolova thực hiện Basic Attack - Movement of Fate and Finality</t>
+          <t>Ảnh Phrolova thực hiện Basic Attack - Điệu Vũ Định Mệnh và Kết Cục</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Chụp ảnh Phrolova thực hiện Resonance Skill</t>
+          <t>Ảnh Phrolova thực hiện Resonance Skill</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Chụp ảnh Camellya thực hiện giai đoạn cuối của Basic Attack</t>
+          <t>Ảnh Camellya thực hiện giai đoạn cuối của Đòn Basic Attack</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Chụp ảnh Camellya thực hiện Resonance Skill</t>
+          <t>Ảnh Camellya sử dụng Resonance Skill</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Chụp ảnh Camellya thực hiện giai đoạn cuối của Basic Attack ở Chế Độ Hoa Nở</t>
+          <t>Ảnh Camellya thực hiện giai đoạn cuối của Đòn Basic Attack trong Trạng Thái Nở Rộ</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Chụp ảnh Iuno thực hiện Plunging Attack</t>
+          <t>Ảnh Iuno thực hiện Tấn Công Lao Xuống</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Chụp ảnh Iuno Thực Hiện Basic Attack Stage 3</t>
+          <t>Ảnh Iuno thực hiện Basic Attack Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Chụp ảnh Iuno thực hiện Resonance Skill</t>
+          <t>Ảnh Iuno sử dụng Resonance Skill</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Chụp ảnh Qiuyuan đang uống nước</t>
+          <t>Ảnh Qiuyuan đang uống rượu</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Chụp ảnh Qiuyuan triệu hồi tre</t>
+          <t>Ảnh Qiuyuan triệu hồi tre trúc</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Chụp ảnh Qiuyuan đội nón tre</t>
+          <t>Ảnh Qiuyuan đội nón tre</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Chụp ảnh Zani Dodgem khiên vào kẻ địch</t>
+          <t>Ảnh Zani ném khiên vào kẻ địch</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Chụp ảnh Zani đang nghỉ ngơi trên ghế</t>
+          <t>Ảnh Zani nghỉ ngơi trên ghế</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Chụp ảnh Zani thực hiện Heavy Slash</t>
+          <t>Ảnh Zani thực hiện Tấn Công mạnh bằng kiếm</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jinhsi ngồi hoặc đứng trên kiếm</t>
+          <t>Ảnh Jinhsi ngồi hoặc đạp lên thanh kiếm của mình</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jinhsi thực hiện động tác chiến đấu trên không ở trạng thái Incarnation</t>
+          <t>Ảnh Jinhsi thực hiện động tác chiến đấu trên không ở trạng thái Hóa Thân</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jinhsi triệu hồi Kẻ Canh Gác Quyết</t>
+          <t>Ảnh Jinhsi triệu hồi Sentinel Jué</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Chụp ảnh Galbrena bắn súng lục lộn ngược</t>
+          <t>Ảnh Galbrena bắn súng khi lộn ngược</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Chụp ảnh Galbrena bắn shotgun</t>
+          <t>Hình ảnh Galbrena bắn shotgun</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Chụp ảnh Galbrena tấn công bằng đôi cánh</t>
+          <t>Ảnh Galbrena tấn công bằng đôi cánh</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jiyan cầm giáo</t>
+          <t>Ảnh Jiyan cầm thương</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jiyan cất Broadblade vào eo khi thực hiện Basic Attack</t>
+          <t>Ảnh Jiyan đeo Lưỡi Kiếm Rộng vào eo khi thực hiện Basic Attack</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Chụp ảnh Jiyan tạo hình Rồng từ gió</t>
+          <t>Ảnh Jiyan tạo hình Rồng từ gió</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Chụp ảnh Phrolova biến hình thành Hecate để tấn công</t>
+          <t>Ảnh Phrolova hóa thân thành Hecate để tấn công</t>
         </is>
       </c>
     </row>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Chụp ảnh Hecate tấn công bằng roi</t>
+          <t>Hình ảnh Hecate tấn công bằng roi</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Chụp ảnh Phrolova khiêu vũ cùng Hecate</t>
+          <t>Ảnh Phrolova nhảy múa cùng Hecate</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Chụp ảnh Camellya ở Chế độ Nở Hoa</t>
+          <t>Ảnh Camellya trong Trạng Thái Nở Rộ</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Chụp ảnh Camellya ở trạng thái bình thường</t>
+          <t>Ảnh Camellya ở trạng thái bình thường</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Chụp ảnh Hoa Crimson</t>
+          <t>Ảnh Crimson Blossom</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Chụp ảnh Iuno sử dụng Moonring</t>
+          <t>Ảnh Iuno sử dụng Moonring</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Chụp ảnh Iuno sử dụng Moonbow</t>
+          <t>Ảnh Iuno sử dụng Moonbow</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Chụp ảnh Iuno nằm trên vũ khí</t>
+          <t>Hình ảnh Iuno nằm trên vũ khí của mình</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Map Resources</t>
+          <t>Bản Đồ Tài Nguyên</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>TD-Kiểm tra quay lui gameplay trong bản sao</t>
+          <t>Kiểm tra quay lui cơ chế trong phụ bản TD</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Ký ức và sự lưu luyến trong tâm trí trở thành miếng mồi, tạo nên một vỏ bọc giả dối gợi nhớ quá khứ. Con đường bên trong đầy hiểm nguy, chỉ một bước sai lầm có thể khiến người ta rơi vào vực sâu không đáy.</t>
+          <t>Ký ức và nỗi ám ảnh trong tâm trí đóng vai trò như chất liệu, tạo nên một vỏ bọc dối lừa gợi nhớ về quá khứ. Con đường bên trong đầy hiểm nguy, chỉ một bước sai lầm có thể đẩy ta vào vực thẳm không đáy.</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Kiểm tra tổng hợp副本</t>
+          <t>Chạy Thử Nghiệm Tổng Hợp Bản Đồ</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>test 子 Challenge 相关测试</t>
+          <t>Thử nghiệm liên quan đến Thử Thách con</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Một cơn gió lạnh lẽo rít qua hang động tối tăm, lối vào hẹp dẫn đến một thế giới bí ẩn. Nhưng hãy cẩn thận, đây cũng là lãnh địa của những thợ săn, ẩn nấp trong bóng tối. Hãy thận trọng khi tiến sâu vào nơi săn mồi của chúng.</t>
+          <t>Gió lạnh rít lên trong hang động tối tăm, lối vào hẹp dẫn đến một thế giới bí ẩn. Nhưng hãy cẩn thận, vì đây cũng là lãnh địa của những kẻ săn mồi, ẩn nấp trong bóng tối. Hãy thận trọng khi tiến sâu vào nơi săn bắn của chúng.</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Hang Ẩn</t>
+          <t>Hang Động Ẩn</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Nhà máy này là một mê cung với những Exile trục trặc và bẫy nguy hiểm. Mục đích duy nhất của nó: sản xuất hàng loạt những con rối đáng sợ. 
+          <t>Nhà máy này là một mê cung của những Exile trục trặc và bẫy nguy hiểm. Mục đích duy nhất của nó: sản xuất hàng loạt những con rối lạnh lẽo. 
 Bẫy nguy hiểm rình rập ở mọi ngóc ngách.</t>
         </is>
       </c>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Nhà Máy Búp Bê</t>
+          <t>Xưởng sản xuất rối</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Camellya Domain</t>
+          <t>Lãnh Địa Camellya</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Map Thử Nghiệm Quái Vật</t>
+          <t>Bản Đồ Thử Nghiệm Quái Vật</t>
         </is>
       </c>
     </row>
@@ -7983,7 +7983,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Xem trước chuyển cảnh Domain</t>
+          <t>Xem trước chuyển cảnh Tổ Tacet</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Hiện thực và định mệnh phai mờ; Công trình và quy luật sụp đổ. Hỗn loạn nuốt chửng tất cả trong ngọn lửa rực cháy, chỉ còn lại đau đớn và thống khổ.</t>
+          <t>Thực tại và vận mệnh phai mờ; công trình và luật lệ sụp đổ. Hỗn loạn nuốt chửng tất cả trong ngọn lửa rực cháy, chỉ còn lại đau đớn và thống khổ.</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Một không gian bí ẩn trong lòng Tượng Vô Vương, nơi ngọn lửa chiến tranh hỗn loạn được sinh ra.</t>
+          <t>Một không gian bí ẩn trong lòng Tượng Vô Vương, nơi ngọn lửa hỗn loạn của chiến tranh được sinh ra.</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Một công trình hoành tráng nằm trên trục trung tâm của Jinzhou. Nó không chỉ đảm nhiệm chức năng tiếp đón quan trọng và thảo luận các vấn đề trọng đại, mà còn là biểu tượng của hy vọng cho người dân Huanglong.</t>
+          <t>Một công trình vĩ đại nằm trên trục trung tâm của Jinzhou. Không chỉ đảm nhiệm chức năng tiếp đón quan trọng và thảo luận các vấn đề trọng đại, nó còn là biểu tượng của hy vọng cho người dân Huanglong.</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Một không gian bí ẩn trong lòng Tượng Vô Vương, nơi ngọn lửa chiến tranh hỗn loạn được sinh ra.</t>
+          <t>Một không gian bí ẩn trong lòng Tượng Vô Vương, nơi ngọn lửa hỗn loạn của chiến tranh được sinh ra.</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Giọt lệ của thiếu nữ bị giam cầm trong khu rừng thì thầm. Linh hồn nàng mãi bị giam giữ và hành hạ bởi những gai đỏ thẫm, được nuôi dưỡng từ hận thù vô tận.</t>
+          <t>Giọt lệ của thiếu nữ bị giam cầm trong khu rừng thì thầm. Linh hồn nàng mãi bị giam giữ, dày vò bởi những gai nhọn đỏ thẫm, được nuôi dưỡng từ hận thù vô tận.</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro này lưu giữ khu rừng dưới ánh trăng như trước khi Tacet Field nuốt chửng nó. Chính ánh sáng ấy cũng tạo ra cơn ác mộng kinh hoàng vào đêm thứ hai.</t>
+          <t>Quả cầu Sonoro này lưu giữ khu rừng dưới ánh trăng như trước khi Tổ Tacet nuốt chửng nó. Chính ánh sáng ấy cũng đã tạo nên cơn ác mộng kinh hoàng vào đêm thứ hai.</t>
         </is>
       </c>
     </row>
@@ -8439,8 +8439,8 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Pháp luật và trật tự đã sụp đổ, xé nát hiện thực và số phận.
-Hãy lắng nghe lời chúng tôi. Chỉ cần tiến thêm một bước nữa, ngươi sẽ được giải thoát.</t>
+          <t>Luật lệ và trật tự đã sụp đổ, xé nát thực tại và định mệnh.
+Hãy lắng nghe lời ta. Chỉ cần tiến thêm một bước nữa, ngươi sẽ được giải thoát.</t>
         </is>
       </c>
     </row>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Quả cầu Sonoro này lưu giữ ánh sáng mặt trời chiếu rọi khu rừng. Khi ngày và đêm giao thoa, nó ngưng tụ thành tinh thể lửa vĩnh cửu.</t>
+          <t>Quả cầu Sonoro này lưu giữ ánh mặt trời rơi trên khu rừng. Khi ngày và đêm giao tranh, nó ngưng kết thành tinh thể lửa vĩnh cửu.</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Quả cầu Sonoro này ghi lại âm thanh không ngừng của vô số động cơ, một bản nhạc nền thường trực cho đô thị sầm uất từng chìm trong biển kim loại nóng chảy.</t>
+          <t>Quả cầu Sonoro này ghi lại âm thanh náo nhiệt bất tận của vô số động cơ, bản nhạc nền bất diệt của đô thị sầm uất từng chìm trong biển kim loại nóng chảy.</t>
         </is>
       </c>
     </row>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Quả cầu Sonoro này lưu giữ tinh hoa của bình minh và hoàng hôn, khi một tinh thể rực lửa xuyên qua khu rừng, thắp sáng xung quanh trong ánh lửa rực rỡ.</t>
+          <t>Quả cầu Sonoro này lưu giữ tinh hoa của bình minh và hoàng hôn, khi tinh thể rực lửa xuyên qua rừng cây, thắp sáng xung quanh trong ánh lửa rực rỡ.</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Một công trình đồ sộ nằm trên trục trung tâm của Jinzhou. Nơi đây lưu giữ những sự kiện quan trọng kể từ khi Jinzhou được thành lập.</t>
+          <t>Một công trình vĩ đại nằm trên trục trung tâm của Jinzhou. Nơi đây lưu giữ mọi sự kiện quan trọng kể từ khi Jinzhou được thành lập.</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Bậc trí giả biết rằng mọi thứ đều hư ảo, nhưng họ sẽ thay thế cái giả bằng cái thật, và học hỏi những bài học từ trận chiến thực sự qua những kịch bản ảo.</t>
+          <t>Bậc trí giả biết mọi thứ đều là giả dối, nhưng họ sẽ thay thế cái giả bằng cái thật, và học được bài học của trận chiến thực sự từ những tình huống ảo.</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Khi đứng trên mảnh đất của SOL-3, bạn được bao quanh bởi những câu chuyện và huyền thoại về quá khứ của nó, trong khi tương lai đang trải dài dưới chân bạn. Trong ánh sáng vô tận này, vô vàn khả năng đang chờ đợi. Nếu bạn chọn tham gia, có thể bạn sẽ tìm thấy câu trả lời cuối cùng. Nhưng đó không phải là giải pháp đến từ bên ngoài; mà nằm sâu trong quá khứ, tiềm năng vô hạn của tương lai, và chính trái tim bạn.</t>
+          <t>Khi đứng trên mảnh đất SOL-3 này, cậu như được bao bọc bởi những huyền thoại và câu chuyện của quá khứ, trong khi tương lai lại trải dài ngay dưới chân. Trong ánh sáng vô tận này, vô vàn khả năng đang chờ đợi. Nếu cậu chọn bước vào, có lẽ cậu sẽ tìm thấy câu trả lời cuối cùng. Nhưng đó không phải là lời giải đến từ bên ngoài, mà nằm sâu trong quá khứ, trong tiềm năng vô hạn của tương lai, và ngay trong trái tim của chính cậu.</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Nơi đây tập trung ánh đèn sân khấu của thế giới, và dưới ánh sáng ấy là những sự thật đang chờ những kẻ dũng cảm khám phá. Hoặc có lẽ câu trả lời luôn ở trong trái tim bạn.</t>
+          <t>Nơi đây tập trung ánh sáng của thế giới, và dưới ánh sáng ấy là những sự thật đang chờ người dũng cảm khám phá. Hoặc có lẽ câu trả lời vẫn luôn ở trong tim cậu.</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Kẻ khôn ngoan coi mọi thứ đều giả dối, trong khi người trí tuệ biến giả dối thành chân thật. Điều này cũng áp dụng cho huấn luyện ảo.</t>
+          <t>Kẻ khôn ngoan coi mọi thứ đều giả dối, còn người trí tuệ biến giả dối thành chân thật. Huấn luyện ảo cũng vậy.</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Một vùng đất bí ẩn từ hư không. Search trên những con đường hẹp để đến đích nơi kho báu ẩn giấu.</t>
+          <t>Một vùng đất bí ẩn xuất hiện từ hư không. Hãy tìm kiếm những lối đi hẹp để đến nơi cất giấu kho báu.</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Một vùng đất bí ẩn từ hư không. Search trên những con đường hẹp để đến đích nơi kho báu ẩn giấu.</t>
+          <t>Một vùng đất bí ẩn xuất hiện từ hư không. Hãy tìm kiếm những lối đi hẹp để đến nơi cất giấu kho báu.</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Phiên Bản Hoạt Động Thử Nghiệm Nhân Vật</t>
+          <t>Phiên Bản Hoạt Động Nhân Vật Thử Nghiệm</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Một cánh cổng bí ẩn xuất hiện tại Bãi Lầy Aix Rên Rỉ, mở ra một thế giới gọi là Somnoire. Tương truyền, nơi đây chứa đựng những giấc mơ của tất cả sinh linh ở Solaris.</t>
+          <t>Một cánh cổng bí ẩn hiện ra tại Đầm Than Vãn Aix, mở lối đến cõi Somnoire. Theo truyền thuyết, nơi đây chứa đựng giấc mơ của mọi sinh linh trên Solaris.</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Một trung tâm nghiên cứu ngầm rộng lớn được xây dựng trước Lament, nổi bật với giếng sâu xuống tới ranh giới Moho. Ở đáy giếng, vô vàn bí ẩn đang chờ được khám phá.</t>
+          <t>Một trung tâm nghiên cứu ngầm rộng lớn được xây dựng trước Lament, có giếng sâu xuống đến tận ranh giới Moho. Ở đáy giếng, những bí ẩn đang chờ được giải đáp.</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Giữa muôn tiếng ồn ào tại cánh cổng dẫn vào thế giới bí ẩn, những lời cầu cứu yếu ớt vẫn cố vươn lên, mong được nghe thấy trong hỗn loạn.</t>
+          <t>Giữa tiếng ồn ào hỗn loạn nơi cổng vào thế giới bí ẩn, những lời cầu cứu yếu ớt vẫn cố vươn lên, mong được nghe thấy trong hỗn độn.</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Tại rìa Rừng Mờ, một hang động hẹp phát ra tiếng ầm ì trầm thấp cùng tiếng gió rít lên mời gọi.</t>
+          <t>Bên rìa Rừng Mờ, một hang động hẹp réo gọi với tiếng gầm trầm và tiếng gió rít.</t>
         </is>
       </c>
     </row>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Ẩn sâu trong lòng một công trình bỏ hoang, một nhà máy cải tạo không ngừng sản xuất những con rối kỳ bí và ma quái.</t>
+          <t>Ẩn sâu trong lòng một công trình bỏ hoang, nhà máy cải tạo không ngừng sản xuất những con rối kỳ bí và ma quái.</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Rơi vật phẩm Squama</t>
+          <t>Vật phẩm rơi Squama</t>
         </is>
       </c>
     </row>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9740,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
     </row>
@@ -9807,7 +9807,7 @@
       <c r="M143" t="inlineStr">
         <is>
           <t>Shilang đang tiến hành nghiên cứu tối ưu hóa tính chất hợp kim.
-Gần đây xuất hiện một Sonoro Sphere độc đáo, và Shilang phát hiện ra rằng các hợp kim ông rèn có khả năng đặc biệt trong lĩnh vực này.</t>
+Gần đây, một Sonoro Sphere độc đáo đã xuất hiện, và Shilang phát hiện ra rằng những hợp kim anh rèn có khả năng đặc biệt trong lĩnh vực này.</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       <c r="M144" t="inlineStr">
         <is>
           <t>Shilang đang tiến hành nghiên cứu tối ưu hóa tính chất hợp kim.
-Gần đây xuất hiện một Sonoro Sphere độc đáo, và Shilang phát hiện ra rằng các hợp kim ông rèn có khả năng đặc biệt trong lĩnh vực này.</t>
+Gần đây, một Sonoro Sphere độc đáo đã xuất hiện, và Shilang phát hiện ra rằng những hợp kim anh rèn có khả năng đặc biệt trong lĩnh vực này.</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Kẻ địch Lv. 30</t>
+          <t>Kẻ địch Cấp 30</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Kẻ địch Lv. 30</t>
+          <t>Kẻ địch Cấp 30</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Quái Lv. 40</t>
+          <t>Kẻ địch Cấp 40</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Quái Lv. 50</t>
+          <t>Kẻ địch Cấp 50</t>
         </is>
       </c>
     </row>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Quái Lv. 60</t>
+          <t>Kẻ địch Cấp 60</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Quái Lv. 70</t>
+          <t>Kẻ địch Cấp 70</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Quái Lv. 80</t>
+          <t>Kẻ địch Cấp 80</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Quái Lv. 90</t>
+          <t>Kẻ địch Cấp 90</t>
         </is>
       </c>
     </row>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Quái Lv. 40</t>
+          <t>Kẻ địch Cấp 40</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Quái Lv. 50</t>
+          <t>Kẻ địch Cấp 50</t>
         </is>
       </c>
     </row>
@@ -10849,7 +10849,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>SOL3 Thăng Tiến Pha</t>
+          <t>Thăng Hoa Giai Đoạn SOL3</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Thử Nghiệm Quái Vật</t>
+          <t>Kiểm tra quái vật</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Tempest Mephis II</t>
+          <t>Mephis Bão Tố II</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11954,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Tempest Mephis I</t>
+          <t>Mephis Bão Tố I</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Tempest Mephis I</t>
+          <t>Mephis Bão Tố I</t>
         </is>
       </c>
     </row>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Tempest Mephis II</t>
+          <t>Mephis Bão Tố II</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Quái Lv. 60</t>
+          <t>Kẻ địch Cấp 60</t>
         </is>
       </c>
     </row>
@@ -12994,7 +12994,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Quái Lv. 70</t>
+          <t>Kẻ địch Cấp 70</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Quái Lv. 80</t>
+          <t>Kẻ địch Cấp 80</t>
         </is>
       </c>
     </row>
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Quái Lv. 90</t>
+          <t>Kẻ địch Cấp 90</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Danh mục</t>
+          <t>Catalog</t>
         </is>
       </c>
     </row>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Mô phỏng Huấn Luyện Combat. Hoàn thành thử thách để nhận nhiều tài nguyên khác nhau.</t>
+          <t>Mô Phỏng Huấn Luyện Chiến Đấu. Hoàn thành thử thách để nhận nhiều tài nguyên khác nhau.</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Một không gian ngầm dùng để thử nghiệm và đánh giá nhiều loại Synth Armaments khác nhau. Xưởng mod ngay bên ngoài khu vực thử nghiệm cho phép người test điều chỉnh và hiệu chỉnh hiệu suất vũ khí trong thời gian thực.</t>
+          <t>Một không gian ngầm dùng để thử nghiệm và đánh giá các loại Synth Armaments. Xưởng sửa đổi ngay bên ngoài khu vực thử nghiệm cho phép người kiểm tra điều chỉnh và hiệu chỉnh hiệu suất vũ khí trong thời gian thực.</t>
         </is>
       </c>
     </row>
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Một cánh cổng bí ẩn xuất hiện tại Bãi Lầy Aix Rên Rỉ, mở ra một thế giới gọi là Somnoire. Tương truyền, nơi đây chứa đựng những giấc mơ của tất cả sinh linh ở Solaris.</t>
+          <t>Một cánh cổng bí ẩn hiện ra tại Đầm Than Vãn Aix, mở lối đến cõi Somnoire. Theo truyền thuyết, nơi đây chứa đựng giấc mơ của mọi sinh linh trên Solaris.</t>
         </is>
       </c>
     </row>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Một cánh cổng bí ẩn xuất hiện tại Bãi Lầy Aix Rên Rỉ, mở ra một thế giới gọi là Somnoire. Tương truyền, nơi đây chứa đựng những giấc mơ của tất cả sinh linh ở Solaris.</t>
+          <t>Một cánh cổng bí ẩn hiện ra tại Đầm Than Vãn Aix, mở lối đến cõi Somnoire. Theo truyền thuyết, nơi đây chứa đựng giấc mơ của mọi sinh linh trên Solaris.</t>
         </is>
       </c>
     </row>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Cấp Độ Thử Nghiệm</t>
+          <t>Cấp Độ Kiểm Tra</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Môi trường mô phỏng TD nhân tạo</t>
+          <t>Môi trường mô phỏng Tổ Tacet nhân tạo</t>
         </is>
       </c>
     </row>
@@ -13644,7 +13644,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>test Crownless 副本2 Rank</t>
+          <t>thử nghiệm Crownless - Phụ bản 2 - Hạng</t>
         </is>
       </c>
     </row>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Crownless - True</t>
+          <t>Crownless - Bản Chính</t>
         </is>
       </c>
     </row>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Nơi từng là bãi thử thách trong lễ trưởng thành để test sức mạnh của người tham gia. Theo thời gian, nó đã trở thành nơi cầu nguyện và ban phước cho Sentinel. Vượt qua thử thách để chứng tỏ bản thân xứng đáng bảo vệ Sentinel và Hongzhen.</t>
+          <t>Từng là địa điểm thử thách trong lễ trưởng thành để kiểm tra sức mạnh của người tham gia. Theo thời gian, nó đã trở thành nơi cầu nguyện và ban phước cho Sentinel. Vượt qua thử thách và chứng tỏ bản thân xứng đáng bảo vệ Sentinel và Hongzhen.</t>
         </is>
       </c>
     </row>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Địa Điểm Cúng Dâng</t>
+          <t>Địa Điểm Dâng Hiến</t>
         </is>
       </c>
     </row>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Nơi từng là bãi thử thách trong lễ trưởng thành để test sức mạnh của người tham gia. Theo thời gian, nó đã trở thành nơi cầu nguyện và ban phước cho Sentinel. Vượt qua thử thách để chứng tỏ bản thân xứng đáng bảo vệ Sentinel và Hongzhen.</t>
+          <t>Từng là địa điểm thử thách trong lễ trưởng thành để kiểm tra sức mạnh của người tham gia. Theo thời gian, nó đã trở thành nơi cầu nguyện và ban phước cho Sentinel. Vượt qua thử thách và chứng tỏ bản thân xứng đáng bảo vệ Sentinel và Hongzhen.</t>
         </is>
       </c>
     </row>
@@ -13970,7 +13970,8 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Để bảo vệ kho báu, khu hầm ngầm của Averardo Vault được thiết kế như một mê cung phức tạp, nơi người ta có thể mãi lạc đường nếu không có sự hướng dẫn. Nếu may mắn, hoặc có lẽ bất hạnh, đưa bạn đến nơi sâu thẳm đó, Echo canh giữ luôn cảnh giác sẽ ở đó, tận tụy thực hiện nhiệm vụ.</t>
+          <t>Để bảo vệ kho báu, khu hầm ngầm của Averardo Vault được thiết kế như một mê cung phức tạp, nơi mà nếu không có người hướng dẫn, kẻ lạc bước có thể mãi mãi không tìm được lối ra. 
+Nếu may mắn, hay có lẽ là bất hạnh, đưa cậu xuống tận sâu thẳm, những Echo canh giữ sẽ luôn ở đó, tận tụy thực hiện nhiệm vụ của mình.</t>
         </is>
       </c>
     </row>
@@ -14035,7 +14036,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Tháp Bỏ Hoang</t>
+          <t>Tháp Bị Bỏ Rơi</t>
         </is>
       </c>
     </row>
@@ -14101,7 +14102,8 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Để bảo vệ kho báu, khu hầm ngầm của Averardo Vault được thiết kế như một mê cung phức tạp, nơi người ta có thể mãi lạc đường nếu không có sự hướng dẫn. Nếu may mắn, hoặc có lẽ bất hạnh, đưa bạn đến nơi sâu thẳm đó, Echo canh giữ luôn cảnh giác sẽ ở đó, tận tụy thực hiện nhiệm vụ.</t>
+          <t>Để bảo vệ kho báu, khu hầm ngầm của Averardo Vault được thiết kế như một mê cung phức tạp, nơi mà nếu không có người hướng dẫn, kẻ lạc bước có thể mãi mãi không tìm được lối ra. 
+Nếu may mắn, hay có lẽ là bất hạnh, đưa cậu xuống tận sâu thẳm, những Echo canh giữ sẽ luôn ở đó, tận tụy thực hiện nhiệm vụ của mình.</t>
         </is>
       </c>
     </row>
@@ -14166,7 +14168,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cháy Bỏng Trong Bóng Tối I</t>
+          <t>Giấc Mộng Cháy Đen I</t>
         </is>
       </c>
     </row>
@@ -14231,7 +14233,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cháy Bỏng Trong Bóng Tối II</t>
+          <t>Giấc Mộng Cháy Đen II</t>
         </is>
       </c>
     </row>
@@ -14296,7 +14298,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cháy Bỏng Trong Bóng Tối III</t>
+          <t>Giấc Mộng Cháy Đen III</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14363,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cháy Bỏng Trong Bóng Tối IV</t>
+          <t>Giấc Mộng Cháy Đen IV</t>
         </is>
       </c>
     </row>
@@ -14426,7 +14428,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cháy Bỏng Trong Bóng Tối V</t>
+          <t>Giấc Mộng Cháy Đen V</t>
         </is>
       </c>
     </row>
@@ -14491,7 +14493,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Lửa tối nhảy múa trong Somnoire. Lần này, gần bờ mộng, bạn thoáng thấy một bóng dáng quen thuộc… Ít nhất trong giấc mơ này, tham vọng thiêu đốt thế giới của hắn sẽ mãi bùng cháy.</t>
+          <t>Lửa đen nhảy múa trong Somnoire. Lần này, gần bờ mộng mị, ngươi thoáng thấy một bóng dáng quen thuộc... Ít nhất trong giấc mơ này, tham vọng nhấn chìm thế giới trong biển lửa của hắn sẽ mãi không tắt.</t>
         </is>
       </c>
     </row>
@@ -14556,7 +14558,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Lửa tối nhảy múa trong Somnoire. Lần này, gần bờ mộng, bạn thoáng thấy một bóng dáng quen thuộc… Ít nhất trong giấc mơ này, tham vọng thiêu đốt thế giới của hắn sẽ mãi bùng cháy.</t>
+          <t>Lửa đen nhảy múa trong Somnoire. Lần này, gần bờ mộng mị, ngươi thoáng thấy một bóng dáng quen thuộc... Ít nhất trong giấc mơ này, tham vọng nhấn chìm thế giới trong biển lửa của hắn sẽ mãi không tắt.</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14623,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Lửa tối nhảy múa trong Somnoire. Lần này, gần bờ mộng, bạn thoáng thấy một bóng dáng quen thuộc… Ít nhất trong giấc mơ này, tham vọng thiêu đốt thế giới của hắn sẽ mãi bùng cháy.</t>
+          <t>Lửa đen nhảy múa trong Somnoire. Lần này, gần bờ mộng mị, ngươi thoáng thấy một bóng dáng quen thuộc... Ít nhất trong giấc mơ này, tham vọng nhấn chìm thế giới trong biển lửa của hắn sẽ mãi không tắt.</t>
         </is>
       </c>
     </row>
@@ -14686,7 +14688,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Lửa tối nhảy múa trong Somnoire. Lần này, gần bờ mộng, bạn thoáng thấy một bóng dáng quen thuộc… Ít nhất trong giấc mơ này, tham vọng thiêu đốt thế giới của hắn sẽ mãi bùng cháy.</t>
+          <t>Lửa đen nhảy múa trong Somnoire. Lần này, gần bờ mộng mị, ngươi thoáng thấy một bóng dáng quen thuộc... Ít nhất trong giấc mơ này, tham vọng nhấn chìm thế giới trong biển lửa của hắn sẽ mãi không tắt.</t>
         </is>
       </c>
     </row>
@@ -14751,7 +14753,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Lửa tối nhảy múa trong Somnoire. Lần này, gần bờ mộng, bạn thoáng thấy một bóng dáng quen thuộc… Ít nhất trong giấc mơ này, tham vọng thiêu đốt thế giới của hắn sẽ mãi bùng cháy.</t>
+          <t>Lửa đen nhảy múa trong Somnoire. Lần này, gần bờ mộng mị, ngươi thoáng thấy một bóng dáng quen thuộc... Ít nhất trong giấc mơ này, tham vọng nhấn chìm thế giới trong biển lửa của hắn sẽ mãi không tắt.</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14818,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Một cõi nơi dòng chảy thời gian hỗn loạn, bình minh và hoàng hôn đan xen. Nó tượng trưng cho cả khởi nguồn lẫn đỉnh cao của trật tự thời gian.</t>
+          <t>Một cõi nơi dòng chảy thời gian hỗn loạn, bình minh và hoàng hôn đan xen. Nó vừa là khởi nguồn, vừa là đỉnh cao của trật tự thời gian.</t>
         </is>
       </c>
     </row>
@@ -14947,8 +14949,8 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Temporal Loop, đấu trường của định mệnh, lại một lần nữa vẫy gọi bạn.
-Vị thần nắm giữ sức mạnh thiên thượng đang kiên nhẫn chờ đợi một trận chiến định mệnh.</t>
+          <t>Vòng Lặp Thời Gian, đấu trường của số phận, lại một lần nữa vẫy gọi ngươi.
+Vị thần nắm giữ sức mạnh thiên giới đang kiên nhẫn chờ đợi trận chiến định mệnh.</t>
         </is>
       </c>
     </row>
@@ -15013,7 +15015,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Chòm Sao Trong Khung Cửa Thời Gian</t>
+          <t>Chòm sao trong Khẩu Độ Thời Gian</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15080,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Vùng đất hoang tàn nơi thời gian trôi hỗn loạn. Được dẫn dắt bởi Ngọn Feather Rực Cháy, với vũ trụ làm bàn cờ và những vì sao làm quân cờ, người được chọn vươn tay chạm vào quá khứ xa xôi dưới Ánh Sáng Vĩnh Cửu.</t>
+          <t>Vùng đất hoang tàn nơi thời gian trôi hỗn loạn. Được dẫn dắt bởi Lông Vũ Rực Cháy, với vũ trụ làm bàn cờ và những vì sao làm quân cờ, người được chọn vươn tay chạm vào quá khứ xa xôi dưới Ánh Sáng Vĩnh Cửu.</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15145,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Trên vùng đất hoang vu nơi thời gian chảy xiết, những chiếc lông vũ rực lửa dẫn lối trên bàn cờ với những vì sao là quân cờ. Nơi đây, người được định mệnh vươn tay chạm vào quá khứ xa xăm dưới ngọn lửa.</t>
+          <t>Trên vùng đất hoang vu nơi thời gian chảy xiết, những chiếc lông vũ rực lửa dẫn đường trên bàn cờ sao trời. Nơi đây, kẻ định mệnh vươn tay chạm vào quá khứ xa xăm dưới ngọn lửa.</t>
         </is>
       </c>
     </row>
@@ -15208,7 +15210,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Phòng Trưng Bày Tro Tàn</t>
+          <t>Phòng Trưng bày Tro Đen</t>
         </is>
       </c>
     </row>
@@ -15273,7 +15275,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Bản sao méo mó của bức tranh đã tạo ra một thế giới ảo qua Forte của người họa sĩ. Những cảm xúc tiêu cực ăn sâu đã ăn mòn màu sắc của nó và khiến các Tacet Discord mạnh mẽ trở nên sống động.</t>
+          <t>Bản sao méo mó của bức tranh đã tạo ra một cõi ảo ảnh nhờ Khả Năng của người họa sĩ. Những cảm xúc tiêu cực ăn sâu đã làm hoen ố màu sắc và khiến các Tacet Discord hùng mạnh trỗi dậy.</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15340,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Bản sao méo mó của bức tranh đã tạo ra một thế giới ảo qua Forte của người họa sĩ. Những cảm xúc tiêu cực ăn sâu đã ăn mòn màu sắc của nó và khiến các Tacet Discord mạnh mẽ trở nên sống động.</t>
+          <t>Bản sao méo mó của bức tranh đã tạo ra một cõi ảo ảnh nhờ Khả Năng của người họa sĩ. Những cảm xúc tiêu cực ăn sâu đã làm hoen ố màu sắc và khiến các Tacet Discord hùng mạnh trỗi dậy.</t>
         </is>
       </c>
     </row>
@@ -15403,7 +15405,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Trích Đoạn Của Sự Điên Cuồng</t>
+          <t>Những Trích Đoạn Cuồng Loạn</t>
         </is>
       </c>
     </row>
@@ -15468,7 +15470,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Những điều ước đã thành hiện thực bị bóp méo thành vỏ rỗng, vang vọng những lời cuồng điên ám ảnh. Những lời thì thầm bị bóp nghẹt và cảm xúc chằng chịt đan xen, tạo nên Sonoro Sphere này. Những căn phòng nối tiếp nhau nhưng đứt đoạn dẫn kẻ xâm nhập trở về điểm khởi đầu của ký ức, nơi tiếng cuồng điên đầu tiên vang lên...</t>
+          <t>Những điều ước đã thành hiện thực bị bóp méo thành những vỏ trống rỗng, vang vọng những lời cuồng loạn ám ảnh. Những tiếng thì thầm bị bóp nghẹt và cảm xúc chằng chịt đan xen, tạo nên Sonoro Sphere này. Những căn phòng nối tiếp nhau nhưng đứt đoạn dẫn lối kẻ xâm nhập trở về điểm khởi đầu của ký ức, nơi tiếng gào thét đầu tiên vang lên...</t>
         </is>
       </c>
     </row>
@@ -15533,7 +15535,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Cục An Ninh Công Cộng đã thiết lập phòng này để giải quyết các xung đột dân sự. Tại đây, các bên tranh chấp có thể tranh luận, hòa giải và đàm phán, giúp việc giải quyết xung đột hiệu quả hơn và đôi khi hỗ trợ điều tra các vụ án lớn.</t>
+          <t>Cục An ninh Công cộng đã thiết lập phòng này để giải quyết các mâu thuẫn dân sự. Tại đây, các bên tranh chấp có thể tranh luận, hòa giải và đàm phán, giúp việc giải quyết xung đột hiệu quả hơn và đôi khi hỗ trợ điều tra các vụ án lớn.</t>
         </is>
       </c>
     </row>
@@ -15663,7 +15665,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Cục An Ninh Công Cộng đã thiết lập phòng này để giải quyết các xung đột dân sự. Tại đây, các bên tranh chấp có thể tranh luận, hòa giải và đàm phán, giúp việc giải quyết xung đột hiệu quả hơn và đôi khi hỗ trợ điều tra các vụ án lớn.</t>
+          <t>Cục An ninh Công cộng đã thiết lập phòng này để giải quyết các mâu thuẫn dân sự. Tại đây, các bên tranh chấp có thể tranh luận, hòa giải và đàm phán, giúp việc giải quyết xung đột hiệu quả hơn và đôi khi hỗ trợ điều tra các vụ án lớn.</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15730,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Trong những câu chuyện của Encore, Wooly Kingdom là nơi những điều ước thành hiện thực và câu chuyện trở nên sống động. Nếu Cánh Cổng Điều Ước khó nắm bắt trong thế giới thực, có lẽ nó ẩn mình trong một câu chuyện nào đó.</t>
+          <t>Trong những câu chuyện của Encore, Vương Quốc Lông Cừu là nơi những điều ước trở thành hiện thực và câu chuyện trở nên sống động. Nếu Cánh Cổng Điều Ước khó tìm thấy trong thế giới thực, có lẽ nó đang ẩn mình trong một câu chuyện nào đó.</t>
         </is>
       </c>
     </row>
@@ -15793,7 +15795,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Wooly Kingdom</t>
+          <t>Vương Quốc Lông Xù</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15860,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Trong những câu chuyện của Encore, Wooly Kingdom là nơi những điều ước thành hiện thực và câu chuyện trở nên sống động. Nếu Cánh Cổng Điều Ước khó nắm bắt trong thế giới thực, có lẽ nó ẩn mình trong một câu chuyện nào đó.</t>
+          <t>Trong những câu chuyện của Encore, Vương Quốc Lông Cừu là nơi những điều ước trở thành hiện thực và câu chuyện trở nên sống động. Nếu Cánh Cổng Điều Ước khó tìm thấy trong thế giới thực, có lẽ nó đang ẩn mình trong một câu chuyện nào đó.</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15925,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Wooly Kingdom</t>
+          <t>Vương Quốc Lông Xù</t>
         </is>
       </c>
     </row>
@@ -15988,7 +15990,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Ánh sáng trắng chói lòa vẫn còn vương vấn trên khung cửa quá khứ, trong khi nỗi đau bất tận đổ bóng sau cánh cửa nặng trĩu. Ôi, chim trong lồng, ngươi sẽ tìm thấy tự do ở đâu?</t>
+          <t>Ánh sáng trắng chói lòa vẫn còn vương vấn trong khung cửa quá khứ, còn nỗi đau không dứt thì phủ bóng sau cánh cửa nặng trĩu. Ôi, chim trong lồng, ngươi sẽ tìm thấy tự do ở nơi đâu?</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16055,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Hành Lang Đau Khổ</t>
+          <t>Hành Lang Thống Khổ</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16120,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Một bông hồng tinh tế, biểu tượng của tình yêu và sắc đẹp. Cậu có nhớ những mùa hè hạnh phúc tưởng như kéo dài mãi trong tâm trí không?</t>
+          <t>Một bông hồng mong manh, biểu tượng của tình yêu và sắc đẹp. Cậu còn nhớ những mùa hè hạnh phúc tưởng như kéo dài mãi mãi trong ký ức không?</t>
         </is>
       </c>
     </row>
@@ -16248,7 +16250,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Một bông hồng tinh tế, biểu tượng của tình yêu và sắc đẹp. Cậu có nhớ những mùa hè hạnh phúc tưởng như kéo dài mãi trong tâm trí không?</t>
+          <t>Một bông hồng mong manh, biểu tượng của tình yêu và sắc đẹp. Cậu còn nhớ những mùa hè hạnh phúc tưởng như kéo dài mãi mãi trong ký ức không?</t>
         </is>
       </c>
     </row>
@@ -16378,7 +16380,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Trong những câu chuyện của Encore, Wooly Kingdom là nơi những điều ước thành hiện thực và câu chuyện trở nên sống động. Nếu Cánh Cổng Điều Ước khó nắm bắt trong thế giới thực, có lẽ nó ẩn mình trong một câu chuyện nào đó.</t>
+          <t>Trong những câu chuyện của Encore, Vương Quốc Lông Cừu là nơi những điều ước trở thành hiện thực và câu chuyện trở nên sống động. Nếu Cánh Cổng Điều Ước khó tìm thấy trong thế giới thực, có lẽ nó đang ẩn mình trong một câu chuyện nào đó.</t>
         </is>
       </c>
     </row>
@@ -16443,7 +16445,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Trong những câu chuyện của Encore, Wooly Kingdom là nơi những điều ước thành hiện thực và câu chuyện trở nên sống động. Nếu Cánh Cổng Điều Ước khó nắm bắt trong thế giới thực, có lẽ nó ẩn mình trong một câu chuyện nào đó.</t>
+          <t>Trong những câu chuyện của Encore, Vương Quốc Lông Cừu là nơi những điều ước trở thành hiện thực và câu chuyện trở nên sống động. Nếu Cánh Cổng Điều Ước khó tìm thấy trong thế giới thực, có lẽ nó đang ẩn mình trong một câu chuyện nào đó.</t>
         </is>
       </c>
     </row>
@@ -16508,7 +16510,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Ánh sáng trắng chói lòa vẫn còn vương vấn trên khung cửa quá khứ, trong khi nỗi đau bất tận đổ bóng sau cánh cửa nặng trĩu. Ôi, chim trong lồng, ngươi sẽ tìm thấy tự do ở đâu?</t>
+          <t>Ánh sáng trắng chói lòa vẫn còn vương vấn trong khung cửa quá khứ, còn nỗi đau không dứt thì phủ bóng sau cánh cửa nặng trĩu. Ôi, chim trong lồng, ngươi sẽ tìm thấy tự do ở nơi đâu?</t>
         </is>
       </c>
     </row>
@@ -16573,7 +16575,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Một bông hồng tinh tế, biểu tượng của tình yêu và sắc đẹp. Cậu có nhớ những mùa hè hạnh phúc tưởng như kéo dài mãi trong tâm trí không?</t>
+          <t>Một bông hồng mong manh, biểu tượng của tình yêu và sắc đẹp. Cậu còn nhớ những mùa hè hạnh phúc tưởng như kéo dài mãi mãi trong ký ức không?</t>
         </is>
       </c>
     </row>
@@ -16638,7 +16640,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Không gian dữ liệu bên trong Stellar Matrix bị hỏng. Sau khi thoát khỏi Error Cell, cấu trúc dữ liệu này bắt đầu hành trình vào sâu trong các vì sao. Dữ liệu bên trong đã bung ra thành một mạng lưới vô tận những khả năng đan xen.</t>
+          <t>Không gian dữ liệu bên trong Stellar Matrix bị hỏng. Sau khi thoát khỏi Error Cell, cấu trúc dữ liệu này bắt đầu hành trình vào sâu trong vũ trụ. Dữ liệu bên trong đã phân rã thành một mạng lưới vô tận các khả năng đan xen.</t>
         </is>
       </c>
     </row>
@@ -16703,7 +16705,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Corrupted Stellar Matrix</t>
+          <t>Ma Trận Stellar Bị Nhiễm Độc</t>
         </is>
       </c>
     </row>
@@ -16768,7 +16770,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Không gian dữ liệu bên trong Stellar Matrix bị hỏng. Sau khi thoát khỏi Error Cell, cấu trúc dữ liệu này bắt đầu hành trình vào sâu trong các vì sao. Dữ liệu bên trong đã bung ra thành một mạng lưới vô tận những khả năng đan xen.</t>
+          <t>Không gian dữ liệu bên trong Stellar Matrix bị hỏng. Sau khi thoát khỏi Error Cell, cấu trúc dữ liệu này bắt đầu hành trình vào sâu trong vũ trụ. Dữ liệu bên trong đã phân rã thành một mạng lưới vô tận các khả năng đan xen.</t>
         </is>
       </c>
     </row>
@@ -16833,7 +16835,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Corrupted Stellar Matrix</t>
+          <t>Ma Trận Stellar Bị Nhiễm Độc</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16900,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Không gian dữ liệu bên trong Ma Trận Sao Đối Xứng. Dữ liệu bên trong Ma Trận Sao Đối Xứng, bản sao của Ma Trận Sao Đã Nhiễm Độc, cũng phân nhánh thành vô số khả năng đan xen; người ta có thể tiến vào Ma Trận Sao Đã Nhiễm Độc thông qua Ma Trận Sao Đối Xứng.</t>
+          <t>Không gian dữ liệu bên trong Stellar Matrix đối xứng. Dữ liệu trong Stellar Matrix đối xứng—bản sao của Stellar Matrix bị hỏng—cũng phân nhánh thành vô số khả năng đan xen; ta có thể tiến vào Stellar Matrix bị hỏng thông qua Stellar Matrix đối xứng.</t>
         </is>
       </c>
     </row>
@@ -17028,7 +17030,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Một Cánh Cổng Sao nằm trong Modulation Hall, cung cấp lối vào sâu thẳm của các vì sao.</t>
+          <t>Một Cổng Sao nằm trong Đại Sảnh Điều Chỉnh, mở đường đến những vực sâu của vũ trụ.</t>
         </is>
       </c>
     </row>
@@ -17093,7 +17095,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Một Cánh Cổng Sao nằm trong Modulation Hall, cung cấp lối vào sâu thẳm của các vì sao.</t>
+          <t>Một Cổng Sao nằm trong Đại Sảnh Điều Chỉnh, mở đường đến những vực sâu của vũ trụ.</t>
         </is>
       </c>
     </row>
@@ -17158,7 +17160,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Một Cánh Cổng Sao nằm trong Modulation Hall, cung cấp lối vào sâu thẳm của các vì sao.</t>
+          <t>Một Cổng Sao nằm trong Đại Sảnh Điều Chỉnh, mở đường đến những vực sâu của vũ trụ.</t>
         </is>
       </c>
     </row>
@@ -17223,7 +17225,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Boss Battle Narwhal</t>
+          <t>Trận chiến Narwhal Boss</t>
         </is>
       </c>
     </row>
@@ -17288,7 +17290,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Lễ Hội Trong Xứ Giấc Mơ I</t>
+          <t>Lễ Hội Ở Slumberland I</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17355,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Carnival Giấc Mơ II</t>
+          <t>Lễ Hội Giấc Mơ II</t>
         </is>
       </c>
     </row>
@@ -17418,7 +17420,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Carnival Giấc Mộng III</t>
+          <t>Lễ Hội Giấc Mơ III</t>
         </is>
       </c>
     </row>
@@ -17483,7 +17485,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Carnival Giấc Mộng IV</t>
+          <t>Lễ Hội Giấc Mơ IV</t>
         </is>
       </c>
     </row>
@@ -17548,7 +17550,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Lễ Hội Trong Xứ Giấc Mơ V</t>
+          <t>Lễ Hội Giấc Mơ V</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17615,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Carnival Giấc Mơ VI: Chaos</t>
+          <t>Lễ Hội Giấc Mơ VI: Hỗn Loạn</t>
         </is>
       </c>
     </row>
@@ -17678,7 +17680,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Hạ xuống vực sâu của Somnoire, vực sâu của giấc mơ. Nơi đây, hỗn loạn và tiếng ồn ngự trị. Bạn chứng kiến toàn bộ cấu trúc nơi này sụp đổ trước mắt. Bạn tiến sâu hơn vào giấc mơ, và một lời thì thầm nhẹ nhàng vuốt ve đôi tai... Trong vương quốc của những giấc mơ, chỉ có giấc mơ mới nắm giữ câu trả lời chúng ta tìm kiếm.</t>
+          <t>Hãy xuống sâu hơn vào Somnoire, vào sâu hơn giấc mơ. Nơi đây, hỗn loạn và tiếng động ngự trị. Ngươi chứng kiến cả không gian này sụp đổ trước mắt. Ngươi tiến sâu hơn vào giấc mơ, và một lời thì thầm nhẹ nhàng vuốt ve đôi tai... Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời ta tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -17743,7 +17745,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Hạ xuống vực sâu của Somnoire, vực sâu của giấc mơ. Nơi đây, hỗn loạn và tiếng ồn ngự trị. Bạn chứng kiến toàn bộ cấu trúc nơi này sụp đổ trước mắt. Bạn tiến sâu hơn vào giấc mơ, và một lời thì thầm nhẹ nhàng vuốt ve đôi tai... Trong vương quốc của những giấc mơ, chỉ có giấc mơ mới nắm giữ câu trả lời chúng ta tìm kiếm.</t>
+          <t>Hãy xuống sâu hơn vào Somnoire, vào sâu hơn giấc mơ. Nơi đây, hỗn loạn và tiếng động ngự trị. Ngươi chứng kiến cả không gian này sụp đổ trước mắt. Ngươi tiến sâu hơn vào giấc mơ, và một lời thì thầm nhẹ nhàng vuốt ve đôi tai... Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời ta tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -17808,7 +17810,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Hạ xuống vực sâu của Somnoire, vực sâu của giấc mơ. Nơi đây, hỗn loạn và tiếng ồn ngự trị. Bạn chứng kiến toàn bộ cấu trúc nơi này sụp đổ trước mắt. Bạn tiến sâu hơn vào giấc mơ, và một lời thì thầm nhẹ nhàng vuốt ve đôi tai... Trong vương quốc của những giấc mơ, chỉ có giấc mơ mới nắm giữ câu trả lời chúng ta tìm kiếm.</t>
+          <t>Hãy xuống sâu hơn vào Somnoire, vào sâu hơn giấc mơ. Nơi đây, hỗn loạn và tiếng động ngự trị. Ngươi chứng kiến cả không gian này sụp đổ trước mắt. Ngươi tiến sâu hơn vào giấc mơ, và một lời thì thầm nhẹ nhàng vuốt ve đôi tai... Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời ta tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -17873,7 +17875,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Hạ xuống vực sâu của Somnoire, vực sâu của giấc mơ. Nơi đây, hỗn loạn và tiếng ồn ngự trị. Bạn chứng kiến toàn bộ cấu trúc nơi này sụp đổ trước mắt. Bạn tiến sâu hơn vào giấc mơ, và một lời thì thầm nhẹ nhàng vuốt ve đôi tai... Trong vương quốc của những giấc mơ, chỉ có giấc mơ mới nắm giữ câu trả lời chúng ta tìm kiếm.</t>
+          <t>Hãy xuống sâu hơn vào Somnoire, vào sâu hơn giấc mơ. Nơi đây, hỗn loạn và tiếng động ngự trị. Ngươi chứng kiến cả không gian này sụp đổ trước mắt. Ngươi tiến sâu hơn vào giấc mơ, và một lời thì thầm nhẹ nhàng vuốt ve đôi tai... Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời ta tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -17938,7 +17940,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Hạ xuống vực sâu của Somnoire, vực sâu của giấc mơ. Nơi đây, hỗn loạn và tiếng ồn ngự trị. Bạn chứng kiến toàn bộ cấu trúc nơi này sụp đổ trước mắt. Bạn tiến sâu hơn vào giấc mơ, và một lời thì thầm nhẹ nhàng vuốt ve đôi tai... Trong vương quốc của những giấc mơ, chỉ có giấc mơ mới nắm giữ câu trả lời chúng ta tìm kiếm.</t>
+          <t>Hãy xuống sâu hơn vào Somnoire, vào sâu hơn giấc mơ. Nơi đây, hỗn loạn và tiếng động ngự trị. Ngươi chứng kiến cả không gian này sụp đổ trước mắt. Ngươi tiến sâu hơn vào giấc mơ, và một lời thì thầm nhẹ nhàng vuốt ve đôi tai... Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời ta tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -18003,7 +18005,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Bạn chìm vào cõi ngủ, nơi những giấc mơ đan xen và hỗn loạn ngự trị. Ở đây, phương hướng trở nên vô nghĩa. Chỉ có lời thì thầm mờ nhạt bạn từng nghe mới là kim chỉ nam cho con đường đúng đắn... Chỉ có chính giấc mơ mới nắm giữ câu trả lời chúng ta tìm kiếm.</t>
+          <t>Bạn chìm vào cõi mộng, nơi những giấc mơ đan xen và hỗn loạn ngự trị. Phương hướng ở đây chẳng còn ý nghĩa gì. Chỉ có lời thì thầm mơ hồ ngày nào mới là kim chỉ nam dẫn lối đúng đắn... Và chỉ có chính giấc mơ mới nắm giữ câu trả lời ta tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -18068,7 +18070,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Tích Lũy Ảo Ảnh I</t>
+          <t>Ảo Ảnh Hội Tụ I</t>
         </is>
       </c>
     </row>
@@ -18133,7 +18135,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Tích Lũy Ảo Ảnh II</t>
+          <t>Ảo Ảnh Hội Tụ II</t>
         </is>
       </c>
     </row>
@@ -18198,7 +18200,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Tích Lũy Ảo Ảnh III</t>
+          <t>Ảo Ảnh Hội Tụ III</t>
         </is>
       </c>
     </row>
@@ -18263,7 +18265,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Tích Lũy Ảo Ảnh IV: Giấc Mộng Tuyệt Vọng</t>
+          <t>Ảo Ảnh Hội Tụ IV: Giấc Mộng Tuyệt Vọng</t>
         </is>
       </c>
     </row>
@@ -18328,7 +18330,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Phantasm Amass V: Giấc Mơ Hỗn Độn</t>
+          <t>Ảo Ảnh Hội Tụ V: Giấc Mộng Mê Lộ</t>
         </is>
       </c>
     </row>
@@ -18393,7 +18395,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Ảo Tưởng Tích Lũy VI: Giấc Mộng Resolution</t>
+          <t>Ảo Ảnh Hội Tụ VI: Giấc Mộng Quyết Tâm</t>
         </is>
       </c>
     </row>
@@ -18458,7 +18460,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Một cõi mộng... với khung cảnh vừa quen vừa lạ. Những bóng ma của quá khứ ẩn náu trong sâu thẳm, ngày càng mạnh mẽ nhờ những giấc mơ chúng nuôi dưỡng. Liệu bạn có còn tìm được lối đi khi ranh giới giữa mộng và thực tan vỡ theo từng bước chân? Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời chúng ta tìm kiếm.</t>
+          <t>Một cõi mộng... nơi quen mà lạ, những bóng hình quá khứ ẩn hiện trong sâu thẳm, lớn dần nhờ giấc mơ chúng nuôi dưỡng. Khi ranh giới giữa mộng và thực tan vỡ dưới từng bước chân, liệu ngươi còn nhận ra lối về? Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời.</t>
         </is>
       </c>
     </row>
@@ -18523,7 +18525,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Một cõi mộng... với khung cảnh vừa quen vừa lạ. Những bóng ma của quá khứ ẩn náu trong sâu thẳm, ngày càng mạnh mẽ nhờ những giấc mơ chúng nuôi dưỡng. Liệu bạn có còn tìm được lối đi khi ranh giới giữa mộng và thực tan vỡ theo từng bước chân? Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời chúng ta tìm kiếm.</t>
+          <t>Một cõi mộng... nơi quen mà lạ, những bóng hình quá khứ ẩn hiện trong sâu thẳm, lớn dần nhờ giấc mơ chúng nuôi dưỡng. Khi ranh giới giữa mộng và thực tan vỡ dưới từng bước chân, liệu ngươi còn nhận ra lối về? Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời.</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18590,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Một cõi mộng... với khung cảnh vừa quen vừa lạ. Những bóng ma của quá khứ ẩn náu trong sâu thẳm, ngày càng mạnh mẽ nhờ những giấc mơ chúng nuôi dưỡng. Liệu bạn có còn tìm được lối đi khi ranh giới giữa mộng và thực tan vỡ theo từng bước chân? Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời chúng ta tìm kiếm.</t>
+          <t>Một cõi mộng... nơi quen mà lạ, những bóng hình quá khứ ẩn hiện trong sâu thẳm, lớn dần nhờ giấc mơ chúng nuôi dưỡng. Khi ranh giới giữa mộng và thực tan vỡ dưới từng bước chân, liệu ngươi còn nhận ra lối về? Trong cõi mộng, chỉ có giấc mơ mới nắm giữ câu trả lời.</t>
         </is>
       </c>
     </row>
@@ -18653,7 +18655,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Những nỗi ám ảnh dai dẳng bám víu, ký ức không chịu phai mờ... lặp lại theo cách méo mó của chúng. Dù có bạn đồng hành bên cạnh, con đường phía trước vẫn là một hành trình tuyệt vọng để trở về nhà…</t>
+          <t>Những nỗi ám ảnh dai dẳng bám víu, ký ức không chịu phai mờ… cứ lặp đi lặp lại theo cách méo mó của chúng. Ngươi có bạn đồng hành bên cạnh, nhưng con đường phía trước là một hành trình trở về nhà đầy tuyệt vọng…</t>
         </is>
       </c>
     </row>
@@ -18718,7 +18720,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Khi những nỗi ám ảnh dần tan biến trong tâm trí, những giấc mơ hỗn loạn cũng vỡ vụn. Nhưng lời thì thầm chia ly lại hòa thành một bản hợp xướng vang dội. Dưới ánh trăng sáng, hãy chứng kiến hành trình cuối cùng này.</t>
+          <t>Khi những nỗi ám ảnh dần phai mờ trong tâm trí, những giấc mơ hỗn loạn vỡ vụn. Nhưng tiếng thì thầm của sự chia ly lại hòa thành một bản hợp xướng vang dội. Dưới ánh trăng sáng, hãy chứng kiến hành trình cuối cùng này.</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18785,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Cơn bão còn lâu mới kết thúc, khi không gian tan vỡ tràn ngập những ảo ảnh vỡ vụn. Sự cân bằng sụp đổ đang chờ được khôi phục, nhưng dù đêm dài đến đâu, các ngươi sẽ lại gặp nhau dưới ánh sáng ban ngày.</t>
+          <t>Cơn bão còn lâu mới kết thúc, khi không gian tan vỡ tràn ngập những ảo ảnh vỡ vụn. Cân bằng sụp đổ đang chờ được hồi sinh, nhưng dù đêm dài đến đâu, các ngươi sẽ lại gặp nhau dưới ánh bình minh.</t>
         </is>
       </c>
     </row>
@@ -18850,9 +18852,9 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào trận chiến.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -18919,9 +18921,9 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào trận chiến.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -18989,10 +18991,10 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào chiến đấu.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Xoáy: Phục hồi 20 Resonance Energy cho bản thân sau khi Dodge thành công. Có thể kích hoạt 1 lần mỗi 5 giây.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Xoáy: Hồi phục 20 Năng lượng Cộng hưởng cho bản thân sau khi né thành công. Có thể kích hoạt 1 lần mỗi 5 giây.</t>
         </is>
       </c>
     </row>
@@ -19060,10 +19062,10 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào chiến đấu.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Xoáy: Phục hồi 20 Resonance Energy cho bản thân sau khi Dodge thành công. Có thể kích hoạt 1 lần mỗi 5 giây.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Xoáy: Hồi phục 20 Năng lượng Cộng hưởng cho bản thân sau khi né thành công. Có thể kích hoạt 1 lần mỗi 5 giây.</t>
         </is>
       </c>
     </row>
@@ -19131,10 +19133,10 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào trận.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Suy yếu: Cứ sau 15 giây khi trận đấu bắt đầu, kẻ địch chịu thêm 40% DMG trong 5 giây.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Yếu ớt: Sau mỗi 15 giây kể từ khi trận đấu bắt đầu, kẻ địch chịu thêm 40% sát thương trong 5 giây.</t>
         </is>
       </c>
     </row>
@@ -19202,10 +19204,10 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào trận.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Suy yếu: Cứ sau 15 giây khi trận đấu bắt đầu, kẻ địch chịu thêm 40% DMG trong 5 giây.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Yếu ớt: Sau mỗi 15 giây kể từ khi trận đấu bắt đầu, kẻ địch chịu thêm 40% sát thương trong 5 giây.</t>
         </is>
       </c>
     </row>
@@ -19272,8 +19274,8 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Bạn tìm thấy Cosmos, người bạn lông lá của Encore, bên cạnh một cánh cổng bí ẩn. Có vẻ như một loại thử nghiệm đang diễn ra phía sau cánh cổng và cần sự trợ giúp của bạn.
-Trong thử nghiệm, Cosmos sẽ cung cấp Echoid để tăng cường đáng kể sức mạnh chiến đấu của Resonators.
+          <t>Bạn tìm thấy Cosmos, người bạn lông lá của Encore, bên cạnh một cánh cổng bí ẩn. Có vẻ như một bài kiểm tra nào đó đang diễn ra phía sau cánh cổng và cần sự trợ giúp của bạn.
+Trong quá trình kiểm tra, Cosmos sẽ cung cấp Echoid để tăng cường đáng kể sức chiến đấu của Resonator.
 Bạn có thể hoàn thành nhiệm vụ cùng bạn bè.</t>
         </is>
       </c>
@@ -19340,8 +19342,8 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Một cánh cổng dẫn đến thế giới mộng mơ, nơi đàn cừu nhảy qua hàng rào nối đuôi nhau, khiến bạn cảm thấy buồn ngủ.
-Hãy bảo vệ thiết bị thí nghiệm và giúp Cosmos hoàn thành bài test.</t>
+          <t>Một cánh cổng dẫn vào thế giới giấc mơ, nơi đàn cừu nhảy qua hàng rào nối tiếp nhau, khiến bạn cảm thấy buồn ngủ.
+Hãy bảo vệ thiết bị thí nghiệm và giúp Cosmos hoàn thành bài kiểm tra.</t>
         </is>
       </c>
     </row>
@@ -19407,8 +19409,8 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Ngay cả khi nhắm mắt, bạn vẫn có thể nghe thấy âm thanh xung quanh. Đây có lẽ là điều người ta gọi là suy nhược thần kinh.
-Hãy bảo vệ thiết bị thí nghiệm và giúp Cosmos hoàn thành bài test.</t>
+          <t>Dù nhắm mắt lại, cậu vẫn nghe thấy âm thanh xung quanh. Có lẽ người ta gọi đó là suy nhược thần kinh.
+Hãy bảo vệ thiết bị thí nghiệm và giúp Cosmos hoàn thành bài kiểm tra.</t>
         </is>
       </c>
     </row>
@@ -19474,8 +19476,8 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Khi thời gian chậm lại, sóng ánh sáng bị kéo dài—có lẽ trong đó ẩn chứa câu trả lời tối thượng cho vũ trụ.
-Hãy bảo vệ thiết bị thí nghiệm và giúp Cosmos hoàn thành bài test.</t>
+          <t>Khi thời gian chậm lại, sóng ánh sáng bị kéo dài—có lẽ chính ở đó ẩn chứa câu trả lời tối thượng của vũ trụ.
+Hãy bảo vệ thiết bị thí nghiệm và giúp Cosmos hoàn thành thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -19541,8 +19543,8 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Trong bóng tối, ai đó thốt lên: "Con người không hiểu số phận, nên ta đã tự mình trở thành số phận."
-Hãy bảo vệ thiết bị thử nghiệm và giúp Cosmos hoàn thành bài test.</t>
+          <t>Trong bóng tối, ai đó thốt lên: "Con người không hiểu vận mệnh, nên ta đã tự mình trở thành vận mệnh."
+Hãy bảo vệ thiết bị thí nghiệm và giúp Cosmos hoàn thành thử nghiệm.</t>
         </is>
       </c>
     </row>
@@ -19608,8 +19610,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>"Ta đã thấy những chiến hạm bốc cháy ngoài bờ vai Orion. Ta đã ngắm những chùm tia C lấp lánh trong bóng tối gần Cổng Tannhäuser." Giọng nói ấy đã gợi lên một ảo ảnh lung linh trước mắt bạn.
-Hãy bảo vệ thiết bị thử nghiệm và giúp Cosmos hoàn thành bài test.</t>
+          <t>"Ta đã thấy những chiến hạm bốc cháy ngoài bờ vai Orion. Ta đã chứng kiến những tia C-beam lấp lánh trong bóng tối gần Cổng Tannhäuser." Giọng nói của hắn đã gợi lên một ảo ảnh lung linh trước mắt ngươi.</t>
         </is>
       </c>
     </row>
@@ -19675,8 +19676,8 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Không cần phải sợ những lời dối trá, vì thế giới được xây dựng trên chúng.
-Hãy bảo vệ thiết bị thí nghiệm và giúp Cosmos hoàn thành bài test.</t>
+          <t>Không cần phải sợ dối trá, vì thế giới này vốn được xây dựng trên chúng.
+Hãy bảo vệ thiết bị thí nghiệm và giúp Cosmos hoàn thành bài kiểm tra.</t>
         </is>
       </c>
     </row>
@@ -19742,8 +19743,8 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Châm Chọc Chaos:
-Tất cả kẻ địch sẽ nhận 1 tầng &lt;color=highlight&gt;Sarcasm&lt;/color&gt; sau mỗi 15 giây trong trận chiến. Hiệu ứng này có thể cộng dồn tối đa 10 lần, mỗi tầng tăng ATK thêm 20%.</t>
+          <t>Sarcasm của Hỗn Loạn:
+Mọi kẻ địch sẽ nhận một tầng &lt;color=highlight&gt;Sarcasm&lt;/color&gt; mỗi 15 giây trong trận chiến. Hiệu ứng này có thể chồng chất lên đến 10 tầng, mỗi tầng tăng 20% ATK.</t>
         </is>
       </c>
     </row>
@@ -19808,7 +19809,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Đầm Lầy Hẻo Lánh I</t>
+          <t>Bãi Đầm Lầy Hẻo Lánh I</t>
         </is>
       </c>
     </row>
@@ -19873,7 +19874,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Đầm Lầy Hẻo Lánh II</t>
+          <t>Bãi Đầm Lầy Hẻo Lánh II</t>
         </is>
       </c>
     </row>
@@ -19938,7 +19939,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Đầm Lầy Hẻo Lánh III</t>
+          <t>Bãi Đầm Lầy Hẻo Lánh III</t>
         </is>
       </c>
     </row>
@@ -20133,7 +20134,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Hiểm Họa Thủy Triều III</t>
+          <t>Thủy Triều Hiểm Nguy III</t>
         </is>
       </c>
     </row>
@@ -20199,8 +20200,8 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Những bóng ma vẫn lảng vảng nơi hoang dã, lẻn tới phía trước khi nghiêng đầu về phía những lời thì thầm khàn khàn.
-Hộp Cát Thực Tế Vô Tận chiếu một Quả Cầu Sonoro đầy nguy hiểm. Hãy tiến lên một cách thận trọng.</t>
+          <t>Những ảo ảnh vẫn lảng vảng nơi hoang dã, lẻn đi khi nghiêng đầu về phía những tiếng thì thầm khàn khàn.
+Hộp Cát Thực Tại Vô Tận chiếu ra một Sonoro Sphere đầy hiểm nguy. Hãy tiến lên thật thận trọng.</t>
         </is>
       </c>
     </row>
@@ -20266,8 +20267,8 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Chiến tranh sinh ra chiến tranh, đau khổ nuôi dưỡng thêm đau khổ. Trong giấc ngủ im lìm, những hạt giống độc ác nảy mầm.
-Infinite Reality Sandbox chiếu một Sonoro Sphere đầy hiểm nguy. Hãy cẩn trọng khi tiến vào.</t>
+          <t>Chiến tranh sinh ra chiến tranh, đau khổ sinh ra đau khổ. Trong giấc ngủ im lặng, những mầm độc ác sẽ nảy mầm.
+Hộp Cát Thực Tại Vô Tận chiếu lên một Sonoro Sphere đầy hiểm nguy. Hãy tiến lên một cách thận trọng.</t>
         </is>
       </c>
     </row>
@@ -20333,8 +20334,8 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Sự Cộng Hưởng bất an từ tĩnh lặng lên đến đỉnh điểm, ngân vang khúc chiến ca hỗn loạn, trói buộc tất cả trong tầm với vào một sự hòa điệu bất hòa.
-Hộp Cát Thực Tại Vô Tận chiếu ra một Quả Cầu Sonoro đầy hiểm nguy. Hãy tiến lên một cách thận trọng.</t>
+          <t>Sóng Dư Âm bất an từ sự tĩnh lặng vươn lên đỉnh điểm, ngân vang khúc chiến ca hỗn loạn, buộc vạn vật trong tầm với hòa vào một bản giao hưởng bất hòa.
+Hộp Cát Thực Tại Vô Tận chiếu lên một Sonoro Sphere đầy hiểm nguy. Hãy cẩn trọng.</t>
         </is>
       </c>
     </row>
@@ -20400,8 +20401,8 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Khi sóng vỗ từ xa, những kẻ hầu của Ovathrax xuất hiện từ bờ biển, rình rập trong cơn bão.
-Hộp Cát Thực Tế Vô Hạn chiếu một Quả Cầu Sonoro đầy hiểm nguy. Hãy tiến lên một cách thận trọng.</t>
+          <t>Khi sóng vỗ xa xa, những kẻ hầu của Ovathrax trỗi dậy từ bờ biển, lẩn khuất trong cơn bão.
+Infinite Reality Sandbox chiếu một Sonoro Sphere đầy hiểm nguy. Hãy cẩn trọng.</t>
         </is>
       </c>
     </row>
@@ -20467,8 +20468,8 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Khi sóng vỗ về từ xa, những kẻ hầu của Ovathrax trỗi dậy từ bờ biển, lang thang dưới ánh mặt trời.
-Hộp Cát Thực Tại Vô Tận chiếu lên một Sonoro Sphere đầy hiểm nguy. Hãy tiến lên một cách thận trọng.</t>
+          <t>Khi sóng vỗ xa xa, những kẻ hầu của Ovathrax trỗi dậy từ bờ biển, lang thang dưới ánh mặt trời.
+Infinite Reality Sandbox chiếu một Sonoro Sphere đầy hiểm nguy. Hãy cẩn trọng.</t>
         </is>
       </c>
     </row>
@@ -20534,8 +20535,8 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Khi sóng vỗ từ xa, những kẻ hầu của Ovathrax xuất hiện từ bờ biển, phi nước đại trong cơn bão tố.
-Hộp Cát Thực Tại Vô Tận chiếu một Quả Cầu Sonoro đầy hiểm nguy. Hãy tiến lên một cách thận trọng.</t>
+          <t>Khi sóng vỗ xa xa, những kẻ hầu của Ovathrax trỗi dậy từ bờ biển, phi nước đại trong cơn bão.
+Infinite Reality Sandbox chiếu một Sonoro Sphere đầy hiểm nguy. Hãy cẩn trọng.</t>
         </is>
       </c>
     </row>
@@ -20603,10 +20604,10 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Trong loạt thử thách này, bạn được mặc định cấp "Roaming Variable".
--Grapple không bước vào Cooldown trong thời gian ngắn sau khi kích hoạt.
-&lt;color=Highlight&gt;Bạn có thể nhận tối đa 4.000 Tactic Points trong thử thách này.&lt;/color&gt;
-&lt;color=Highlight&gt;Tỷ lệ quy đổi Tactic Points: 1&lt;/color&gt;</t>
+          <t>Trong loạt thử thách này, bạn được mặc định nhận "Biến Số Lưu Động".
+-Kỹ năng Móc Câu sẽ không bước vào trạng thái Hồi Chiêu trong một khoảng thời gian ngắn sau khi kích hoạt.
+&lt;color=Highlight&gt;Bạn có thể nhận tối đa 4.000 Điểm Chiến Thuật trong thử thách này.&lt;/color&gt;
+&lt;color=Highlight&gt;Tỷ lệ chuyển đổi Điểm Chiến Thuật: 1&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20674,10 +20675,10 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Trong loạt thử thách này, bạn được mặc định nhận "Roaming Variable".
--Grapple không bước vào Cooldown trong thời gian ngắn sau khi kích hoạt.
-&lt;color=Highlight&gt;Bạn có thể nhận tối đa 12.000 Tactic Points trong thử thách này.&lt;/color&gt;
-&lt;color=Highlight&gt;Tỷ lệ chuyển đổi Tactic Points: 2&lt;/color&gt;</t>
+          <t>Trong loạt thử thách này, bạn được mặc định nhận "Biến Số Lưu Động".
+-Kỹ năng Móc Câu sẽ không bước vào trạng thái Hồi Chiêu trong một khoảng thời gian ngắn sau khi kích hoạt.
+&lt;color=Highlight&gt;Bạn có thể nhận tối đa 12.000 Điểm Chiến Thuật trong thử thách này.&lt;/color&gt;
+&lt;color=Highlight&gt;Tỷ lệ chuyển đổi Điểm Chiến Thuật: 2&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20744,9 +20745,9 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Trong loạt thử thách này, bạn được mặc định nhận "Roaming Variable".
--Móc câu không bước vào Cooldown trong thời gian ngắn sau khi kích hoạt.
-&lt;color=Highlight&gt;Tỷ lệ chuyển đổi Điểm Chiến thuật: 3&lt;/color&gt;</t>
+          <t>Trong loạt thử thách này, bạn được mặc định nhận "Biến Số Lưu Động".
+-Kỹ năng Móc Câu sẽ không bước vào trạng thái Hồi Chiêu trong một khoảng thời gian ngắn sau khi kích hoạt.
+&lt;color=Highlight&gt;Tỷ lệ chuyển đổi Điểm Chiến Thuật: 3&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20815,11 +20816,11 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Trong loạt thử thách này, bạn được ban "Speeding Variable".
-- Tốc độ di chuyển của Resonator được tăng theo mặc định.
-- Lao nhanh sẽ tung kẻ địch lên không và gây DMG. Hiệu ứng này kéo dài 10 giây và sẽ bị loại bỏ khi chuyển sang Resonator khác, với Cooldown 10 giây.
-&lt;color=Highlight&gt;Bạn có thể nhận tối đa 4.000 Tactic Points trong thử thách này.&lt;/color&gt;
-&lt;color=Highlight&gt;Tỷ lệ quy đổi Tactic Points: 1&lt;/color&gt;</t>
+          <t>Trong loạt thử thách này, bạn được mặc định nhận "Biến Số Tăng Tốc".
+-Tốc độ di chuyển của Resonator được tăng lên mặc định.
+-Lao nhanh sẽ hất tung kẻ địch lên không và gây DMG. Hiệu ứng này kéo dài 10 giây và sẽ bị loại bỏ khi chuyển sang Resonator khác, với thời gian Hồi Chiêu là 10 giây.
+&lt;color=Highlight&gt;Bạn có thể nhận tối đa 4.000 Điểm Chiến Thuật trong thử thách này.&lt;/color&gt;
+&lt;color=Highlight&gt;Tỷ lệ chuyển đổi Điểm Chiến Thuật: 1&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20888,11 +20889,11 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Trong loạt thử thách này, bạn được cấp sẵn "Speeding Variable".
-- Tốc độ di chuyển của Resonator được tăng sẵn
-- Lao nhanh sẽ tung kẻ địch lên không và gây DMG. Hiệu ứng này kéo dài 10 giây và sẽ bị loại bỏ khi chuyển sang Resonator khác, với Cooldown 10 giây.
-&lt;color=Highlight&gt;Bạn có thể nhận tối đa 12.000 Tactic Points trong thử thách này.&lt;/color&gt;
-&lt;color=Highlight&gt;Tỷ lệ quy đổi Tactic Points: 2&lt;/color&gt;</t>
+          <t>Trong loạt thử thách này, bạn được mặc định nhận "Biến Số Tăng Tốc".
+-Tốc độ di chuyển của Resonator được tăng lên mặc định.
+-Lao nhanh sẽ hất tung kẻ địch lên không và gây DMG. Hiệu ứng này kéo dài 10 giây và sẽ bị loại bỏ khi chuyển sang Resonator khác, với thời gian Hồi Chiêu là 10 giây.
+&lt;color=Highlight&gt;Bạn có thể nhận tối đa 12.000 Điểm Chiến Thuật trong thử thách này.&lt;/color&gt;
+&lt;color=Highlight&gt;Tỷ lệ chuyển đổi Điểm Chiến Thuật: 2&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20960,10 +20961,10 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Trong loạt thử thách này, bạn được mặc định nhận "Speeding Variable".
-- Tốc độ di chuyển của Resonator được tăng lên
-- Lao nhanh sẽ tung kẻ địch lên không và gây DMG. Hiệu ứng kéo dài 10 giây và sẽ bị loại bỏ khi chuyển sang Resonator khác, với Cooldown 10 giây.
-&lt;color=Highlight&gt;Tỉ lệ chuyển đổi Điểm Chiến Thuật: 3&lt;/color&gt;</t>
+          <t>Trong loạt thử thách này, bạn được mặc định nhận "Biến Số Tăng Tốc".
+-Tốc độ di chuyển của Resonator được tăng lên mặc định.
+-Lao nhanh sẽ hất tung kẻ địch lên không và gây DMG. Hiệu ứng này kéo dài 10 giây và sẽ bị loại bỏ khi chuyển sang Resonator khác, với thời gian Hồi Chiêu là 10 giây.
+&lt;color=Highlight&gt;Tỷ lệ chuyển đổi Điểm Chiến Thuật: 3&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21029,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Bãi Đầm U Tịch</t>
+          <t>Bãi Đầm Lầy Hẻo Lánh</t>
         </is>
       </c>
     </row>
@@ -21093,7 +21094,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Hiểm Họa Thủy Triều</t>
+          <t>Thủy Triều Hiểm Nguy</t>
         </is>
       </c>
     </row>
@@ -21158,7 +21159,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Sau Trận chiến Norfall Barrens, Black Shores và Huaxu Academy đã hợp tác phát triển Infinite Battle Simulation, một hệ thống huấn luyện mô phỏng nhằm đối phó với những mối đe dọa tiềm tàng từ tần số còn sót lại của Threnody.</t>
+          <t>Sau Trận chiến tại Norfall Barrens, Bờ Biển Đen và Học viện Huaxu đã hợp tác phát triển Hệ thống Mô phỏng Chiến đấu Vô hạn, một hệ thống huấn luyện mô phỏng nhằm đối phó với những mối đe dọa tiềm tàng từ tần số còn sót lại của Threnodian.</t>
         </is>
       </c>
     </row>
@@ -21224,8 +21225,8 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>"Những cuộc phiêu lưu tuyệt vời trong truyện thường bắt đầu bằng một cơn gió bất chợt."
-Hỗ trợ Dorothy đánh bại quái vật sau cánh cổng.</t>
+          <t>"'Những cuộc phiêu lưu vĩ đại trong truyện thường bắt đầu bằng một cơn gió bất chợt.'
+Hãy giúp Dorothy đánh bại lũ quái vật sau cánh cổng."</t>
         </is>
       </c>
     </row>
@@ -21291,8 +21292,8 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>"Hãy bắt đầu cuộc hành trình tìm kiếm giấc mơ. Mong rằng bạn sẽ tìm thấy bản thân thật sự trong thế giới sáng rõ này."
-Giúp Dorothy đánh bại những con quái vật phía sau cánh cổng.</t>
+          <t>"Hãy bắt đầu hành trình tìm kiếm giấc mơ. Mong rằng cậu sẽ tìm thấy bản thân thật sự trong thế giới trong sáng này."
+Giúp Dorothy đánh bại những con quái vật sau cánh cổng.</t>
         </is>
       </c>
     </row>
@@ -21358,8 +21359,8 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>"Dũng cảm chỉ là thứ tiêu hao theo bản chất, càng lớn tuổi thì càng đắt đỏ."
-Giúp Dorothy đánh bại lũ quái sau cánh cổng.</t>
+          <t>"Dũng cảm vốn dĩ chỉ là thứ tiêu hao theo thời gian, càng lớn tuổi, giá của nó càng đắt đỏ."
+Hãy giúp Dorothy đánh bại lũ quái vật sau cánh cổng.</t>
         </is>
       </c>
     </row>
@@ -21492,8 +21493,8 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>"Mặt trời mọc trên những ngôi nhà trong làng. Liệu ngày mai có phải là một ngày mới không nhỉ?"
-Giúp Dorothy đánh bại lũ quái vật phía sau cánh cổng.</t>
+          <t>"Mặt trời mọc trên những ngôi nhà trong làng. Không biết ngày mai có phải là một ngày mới hoàn toàn không nhỉ?"
+Giúp Dorothy đánh bại lũ quái vật sau cánh cổng.</t>
         </is>
       </c>
     </row>
@@ -21559,8 +21560,8 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>"Đã đến lúc nói lời tạm biệt. Đây là nơi tôi sẽ để lại bản thân yếu đuối của quá khứ."
-Giúp Dorothy đánh bại lũ quái vật phía sau cánh cổng.</t>
+          <t>"Đã đến lúc nói lời tạm biệt. Đây là nơi ta sẽ bỏ lại cái tôi yếu đuối của quá khứ."
+Hãy giúp Dorothy đánh bại lũ quái vật sau cánh cổng."</t>
         </is>
       </c>
     </row>
@@ -21627,9 +21628,9 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Bên cạnh một cánh cổng bí ẩn là cô gái Dorothy, vô tình lạc qua đó. Cô ấy cần sự giúp đỡ của bạn để đánh bại những con quái vật ẩn nấp sau cánh cổng.
-Trong thử thách này, bạn có thể chọn "Dorothy's Companions" làm Echoes hỗ trợ trong trận chiến, giúp tăng cường đáng kể sức mạnh chiến đấu của Resonators.
-Bạn có thể hoàn thành nhiệm vụ cùng Bạn bè.</t>
+          <t>Bên cạnh cánh cổng huyền bí là một cô bé vô tình lạc qua đó—Dorothy. Cô bé cầu cứu cậu giúp đánh bại lũ quái vật đang ẩn nấp phía sau.
+Trong thử thách này, cậu có thể chọn "Bạn Đồng Hành của Dorothy" làm Echo hỗ trợ chiến đấu, giúp tăng cường đáng kể khả năng chiến đấu của Resonator.
+Cậu có thể hoàn thành nhiệm vụ cùng bạn bè của mình.</t>
         </is>
       </c>
     </row>
@@ -21695,8 +21696,8 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Được vẽ vào một buổi sáng hè rực rỡ, bức tranh này khắc họa một Lottie Lost đang dạo bước dưới chiếc ô che nắng, làn gió nhẹ nhàng lướt qua. 
-"Ta sẽ so sánh ngươi với một ngày hè chăng?"</t>
+          <t>Được vẽ vào một buổi sáng hè rực rỡ, bức tranh này khắc họa Lottie Lost dạo bước dưới chiếc ô che nắng, làn gió nhẹ nhàng lướt qua. 
+"Ta có nên ví nàng như một ngày hè chăng?"</t>
         </is>
       </c>
     </row>
@@ -21762,8 +21763,8 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Khi Lễ Hội Carnevale vắng bóng, những giấc mơ bất an trôi dạt trong đêm đầy sao ở Ragunna.
-"Đêm đầy sao, đêm đầy sao. Hãy tô lên bảng màu xanh và xám của ngươi."</t>
+          <t>Khi Lễ Hội Carnevale vắng bóng, những giấc mơ bất an trôi dạt trong đêm đầy sao của Ragunna.
+"Đêm đầy sao, đêm đầy sao. Hãy tô bảng màu xanh và xám của ngươi lên."</t>
         </is>
       </c>
     </row>
@@ -21829,8 +21830,8 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Một bức chân dung được tôn vinh là đỉnh cao nghệ thuật của Ragunna, thế nhưng nụ cười của Sứ Giả Thần Linh trên bức vải vẫn là một ẩn số.
-"Tôi không giỏi chụp ảnh, bởi nó chẳng có giá trị gì với một họa sĩ."</t>
+          <t>Bức chân dung được ca ngợi là đỉnh cao nghệ thuật của Ragunna, thế nhưng nụ cười của Sứ giả Thần thánh trên tranh vẫn là một ẩn số.
+"Tôi không giỏi chụp ảnh, vì nó chẳng có giá trị gì với một họa sĩ."</t>
         </is>
       </c>
     </row>
@@ -21896,8 +21897,8 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Qua đôi mắt của người hành hương, biển cả dữ dội chính là hiện thân của đức hạnh và đam mê.
-"Hãy thử tưởng tượng điều gì đó cậu chưa từng thấy và để bàn tay cậu tự do trên bức vải."</t>
+          <t>Qua đôi mắt của người hành hương, biển động chính là hiện thân của đức hạnh và đam mê.
+"Hãy thử tưởng tượng điều gì đó mà con chưa từng thấy và để bàn tay tự do trên bức vải."</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21964,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Trên bức họa, nữ tu sĩ đeo hoa tai ngọc trai nhìn người họa sĩ với ánh mắt vĩnh cửu, sự im lặng của nàng vang vọng.
+          <t>Trên bức họa, nữ tu sĩ đeo hoa tai ngọc trai đang nhìn họa sĩ với ánh mắt vĩnh cửu, sự im lặng của nàng vang vọng.
 "Phải chăng tuổi thanh xuân vàng son của ta đã ban tặng ta những đóa hồng một cách phù phiếm?"</t>
         </is>
       </c>
@@ -22030,8 +22031,8 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Trong thời khắc nguy nan, người dân Ragunna tập hợp dưới ngọn cờ của bà để chống lại quân xâm lược. 
-"Tôn vinh Imperator!"</t>
+          <t>Trong thời khắc nguy nan, người dân Ragunna đoàn kết dưới ngọn cờ của bà để chống lại quân xâm lược. 
+"Vinh quang thuộc về Nữ Hoàng!"</t>
         </is>
       </c>
     </row>
@@ -22097,8 +22098,8 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Người Fisalia không biết về nguồn gốc của Sentinel Imperator, nhưng trong giấc mơ của họ, không có quyền lực nào cao hơn.
-"Im lặng trên những vùng đất hoang và núi non, Họ ra lệnh cho biển đập vào vách đá."</t>
+          <t>Gia tộc Fisalia không biết về nguồn gốc của Sentinel Imperator, nhưng trong giấc mơ của họ, chẳng có quyền lực nào cao hơn.
+"Lặng im trên hoang mạc và núi đồi, Họ ra lệnh cho biển cả đập vào vách đá."</t>
         </is>
       </c>
     </row>
@@ -22165,9 +22166,9 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Bên cạnh một bức tranh morph bí ẩn, bạn gặp một họa sĩ tên Claudia, bị mắc kẹt trong những cơn ác mộng của cô.
-Claudia nhờ bạn điều tra thế giới bên trong bức tranh và đưa cho bạn một lá bùa hộ mệnh. Trong thế giới tranh vẽ, lá bùa biến thành nhiều Echoes khác nhau để hỗ trợ bạn.
-Bạn có thể hoàn thành nhiệm vụ cùng bạn bè.</t>
+          <t>Bên cạnh bức tranh biến ảo kỳ bí, bạn tìm thấy một họa sĩ tên Claudia, bị mắc kẹt trong những cơn ác mộng của chính mình. 
+Claudia nhờ bạn điều tra thế giới bên trong bức tranh và trao cho bạn một lá bùa hộ mệnh. Trong thế giới hội họa, lá bùa biến thành những Echo khác nhau để hỗ trợ bạn.
+Bạn có thể hoàn thành nhiệm vụ này cùng bạn bè.</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22233,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Tiếng Gọi Oan Nghiệt I</t>
+          <t>Lời Triệu Hồi U Minh I</t>
         </is>
       </c>
     </row>
@@ -22297,7 +22298,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>"Họ thích những câu chuyện cậu viết. Nhưng thế giới không tử tế như trong chuyện đâu."</t>
+          <t>"Họ rất thích những câu chuyện cậu viết. Nhưng thế giới này không hề nhân từ như trong chuyện đâu."</t>
         </is>
       </c>
     </row>
@@ -22362,7 +22363,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>"Nỗi đau dâng trào hàn gắn trái tim. Thở dài nặng nề, bạn được tái sinh."</t>
+          <t>"Nỗi đau chồng chất hàn gắn trái tim. Thở dài nặng nề, ngươi được tái sinh."</t>
         </is>
       </c>
     </row>
@@ -22427,7 +22428,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>"Thế giới là một vùng đất hoang rộng lớn, còn anh là con tàu nối liền các thế hệ."</t>
+          <t>"Thế giới là một vùng hoang vu rộng lớn, còn ngươi là đoàn tàu nối liền các thế hệ."</t>
         </is>
       </c>
     </row>
@@ -22492,7 +22493,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>"Thương nhân tầm thường bán sản phẩm. Thương nhân xuất sắc bán giấc mơ."</t>
+          <t>"Thương nhân tầm thường bán hàng hóa. Thương nhân xuất sắc bán giấc mơ."</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22558,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>"Bạn nhận ra rằng mọi thứ rồi cũng sẽ phai mờ theo thời gian. Giống như giọt nước mắt tan biến trong cơn mưa."</t>
+          <t>"Ngươi hiểu rằng mọi thứ rồi cũng sẽ phai mờ theo thời gian. Như giọt nước mắt tan biến trong cơn mưa."</t>
         </is>
       </c>
     </row>
@@ -22622,7 +22623,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>"Kẻ mang mọi cái tên bước vào ngày mai."</t>
+          <t>"Kẻ mang mọi cái tên bước về ngày mai."</t>
         </is>
       </c>
     </row>
@@ -22687,7 +22688,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Solo &amp; Co-op)</t>
+          <t>Thời Gian Hồi Sinh: 10 giây (Solo &amp; Co-op)</t>
         </is>
       </c>
     </row>
@@ -22752,7 +22753,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Solo &amp; Co-op)</t>
+          <t>Thời Gian Hồi Sinh: 10 giây (Solo &amp; Co-op)</t>
         </is>
       </c>
     </row>
@@ -22817,7 +22818,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Solo &amp; Co-op)</t>
+          <t>Thời Gian Hồi Sinh: 10 giây (Solo &amp; Co-op)</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22883,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Solo &amp; Co-op)</t>
+          <t>Thời Gian Hồi Sinh: 10 giây (Solo &amp; Co-op)</t>
         </is>
       </c>
     </row>
@@ -22947,7 +22948,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Solo &amp; Co-op)</t>
+          <t>Thời Gian Hồi Sinh: 10 giây (Solo &amp; Co-op)</t>
         </is>
       </c>
     </row>
@@ -23012,7 +23013,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Solo &amp; Co-op)</t>
+          <t>Thời Gian Hồi Sinh: 10 giây (Solo &amp; Co-op)</t>
         </is>
       </c>
     </row>
@@ -23078,8 +23079,8 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Cooldown Sinh: 15 giây (Solo)/10 giây (Co-op)
-Kẻ địch gây thêm 50% DMG lên mục tiêu có dưới 50% HP.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo)/10 giây (Co-op)
+Kẻ địch gây thêm 50% DMG lên mục tiêu có HP dưới 50%.</t>
         </is>
       </c>
     </row>
@@ -23145,8 +23146,8 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Cooldown Sinh: 15 giây (Solo)/10 giây (Co-op)
-Các đòn tấn công của kẻ địch sẽ bỏ qua 1000 DEF khi HP của nó giảm dưới 50%.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo)/10 giây (Co-op)
+Khi HP dưới 50%, đòn tấn công của kẻ địch xuyên phá 1000 Phòng Ngự.</t>
         </is>
       </c>
     </row>
@@ -23212,7 +23213,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 15 giây (Solo)/10 giây (Co-op)
+          <t>Thời gian hồi sinh: 15 giây (Solo)/10 giây (Co-op)
 Mỗi lần trúng đòn, ATK của kẻ địch tăng 10%, hiệu ứng sẽ bị loại bỏ khi bị bất động.</t>
         </is>
       </c>
@@ -23279,8 +23280,8 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 15 giây (Solo)/10 giây (Hợp tác)
-ATK của kẻ địch tăng 50% trong 60 giây đầu.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo)/10 giây (Co-op)
+Trong 60 giây đầu, ATK của kẻ địch tăng 50%.</t>
         </is>
       </c>
     </row>
@@ -23346,8 +23347,8 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Cooldown Sinh: 15s (Solo)/10s (Co-op)
-Lần đầu HP giảm dưới 50%, kẻ địch sẽ nhận khiên. Nếu khiên vẫn còn sau 30 giây, ATK của chúng tăng 100%.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo)/10 giây (Co-op)
+Kẻ địch nhận Khiên lần đầu khi HP giảm dưới 50%. Nếu Khiên vẫn tồn tại sau 30 giây, ATK của chúng tăng 100%.</t>
         </is>
       </c>
     </row>
@@ -23413,8 +23414,8 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 15 giây (Solo)/10 giây (Co-op)
-Tỉ lệ DMG Reduction của kẻ địch tăng 50%, hiệu ứng này sẽ bị loại bỏ sau khi nó bị bất động lần đầu.</t>
+          <t>Thời gian hồi sinh: 15 giây (Solo)/10 giây (Co-op)
+Giảm Sát Thương nhận vào của kẻ địch tăng 50%, hiệu ứng sẽ bị loại bỏ sau lần đầu bị bất động.</t>
         </is>
       </c>
     </row>
@@ -23480,8 +23481,8 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
-&lt;color=#c25757&gt;Trial Resonators sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+&lt;color=#c25757&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23547,8 +23548,8 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
-&lt;color=#c25757&gt;Trial Resonators sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+&lt;color=#c25757&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23614,8 +23615,8 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Cooldown sinh: 10 giây (Chơi đơn &amp; Đồng đội)
-&lt;color=#c25757&gt;Trial Resonators sẽ khả dụng trong chế độ Chơi đơn.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+&lt;color=#c25757&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23682,9 +23683,9 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Cooldown Sinh: 10s (Solo &amp; Co-op)
-Kẻ địch nhận Shield có giá trị bằng 20% HP tối đa, ATK tăng 70% khi có Shield.
-&lt;color=#c25757&gt;Resonators thử nghiệm sẽ khả dụng trong chế độ Solo.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+Kẻ địch nhận Khiên tương đương 20% HP tối đa, đồng thời ATK tăng 70% khi có Khiên.
+&lt;color=#c25757&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23751,9 +23752,9 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Thời gian Hồi sinh: 10s (Solo &amp; Co-op)
-Kẻ địch bắt đầu với 5 tầng Toughness. Mỗi tầng tăng DEF của chúng lên 20%. Mỗi khi kẻ địch chịu DMG, chúng mất 1 tầng Toughness.
-&lt;color=#c25757&gt;Resonators thử nghiệm sẽ có sẵn trong chế độ Solo.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+Kẻ địch bắt đầu với 5 lớp Kiên Cường. Mỗi lớp tăng Phòng Ngự 20%. Mỗi lần chịu DMG, chúng mất 1 lớp Kiên Cường.
+&lt;color=#c25757&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23820,9 +23821,9 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Cooldown Sinh: 10s (Solo &amp; Co-op)
-Sử dụng Resonance Skill sẽ tiêu hao 20% HP tối đa của Resonators.
-&lt;color=#c25757&gt;Resonators thử nghiệm sẽ khả dụng trong chế độ Solo.&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+Sử dụng Kỹ Năng Echo sẽ tiêu hao 20% HP tối đa của Resonator.
+&lt;color=#c25757&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23889,9 +23890,9 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Cooldown Sinh: 10s (Solo &amp; Co-op)
-Đây là thử thách có độ khó cao. Hãy chuẩn bị kỹ càng. Phần thưởng ẩn đang chờ đón những ai hoàn thành thử thách.
-&lt;color=#c25757&gt;Trial Resonators sẽ khả dụng trong chế độ Solo&lt;/color&gt;</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+Đây là thử thách cực khó. Hãy chuẩn bị kỹ càng. Phần thưởng ẩn đang chờ những ai vượt qua thử thách.
+&lt;color=#c25757&gt;Resonator thử nghiệm sẽ xuất hiện trong chế độ Solo.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23956,7 +23957,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Một Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của Dreamscape Nodes.</t>
+          <t>Một Tacet Discord đặc biệt ẩn nấp trong mạng lưới phức tạp của các Nút Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -24021,7 +24022,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>test/泰缇斯之底-AKIwp</t>
+          <t>Đáy Tacet-AKIwp</t>
         </is>
       </c>
     </row>
@@ -24216,7 +24217,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Thánh Cột Hội Tụ</t>
+          <t>Tháp Thánh Hội Tụ</t>
         </is>
       </c>
     </row>
@@ -24284,10 +24285,10 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào combat.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Hạng Combat: Các hành động chiến đấu của bạn sẽ được tính vào Combat Rank. Dodge thành công, Dodge Counter và Counterattack tăng đáng kể Combat Rank, trong khi bị đánh trúng sẽ làm giảm mạnh Combat Rank.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Xếp hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Xếp hạng Chiến đấu. Né thành công, Phản đòn Né và Phản công sẽ tăng đáng kể Xếp hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Xếp hạng Chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -24355,10 +24356,10 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào chiến đấu.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Hạng Chiến đấu. Dodge thành công, Dodge Counter và Counterattack tăng đáng kể Hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Hạng Chiến đấu.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Xếp hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Xếp hạng Chiến đấu. Né thành công, Phản đòn Né và Phản công sẽ tăng đáng kể Xếp hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Xếp hạng Chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -24426,10 +24427,10 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào chiến đấu.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Hạng Chiến đấu. Dodge thành công, Dodge Counter và Counterattack tăng đáng kể Hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Hạng Chiến đấu.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Xếp hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Xếp hạng Chiến đấu. Né thành công, Phản đòn Né và Phản công sẽ tăng đáng kể Xếp hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Xếp hạng Chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -24497,10 +24498,10 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào chiến đấu.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Hạng Chiến đấu. Dodge thành công, Dodge Counter và Counterattack tăng đáng kể Hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Hạng Chiến đấu.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Xếp hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Xếp hạng Chiến đấu. Né thành công, Phản đòn Né và Phản công sẽ tăng đáng kể Xếp hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Xếp hạng Chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -24568,10 +24569,10 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào chiến đấu.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Hạng Chiến đấu. Dodge thành công, Dodge Counter và Counterattack tăng đáng kể Hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Hạng Chiến đấu.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Xếp hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Xếp hạng Chiến đấu. Né thành công, Phản đòn Né và Phản công sẽ tăng đáng kể Xếp hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Xếp hạng Chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -24639,10 +24640,10 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào chiến đấu.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Hạng Chiến đấu. Dodge thành công, Dodge Counter và Counterattack tăng đáng kể Hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Hạng Chiến đấu.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Xếp hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Xếp hạng Chiến đấu. Né thành công, Phản đòn Né và Phản công sẽ tăng đáng kể Xếp hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Xếp hạng Chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -24710,10 +24711,10 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Mô phỏng: Tất cả kẻ địch có 0 RES trong sự kiện Tactical Simulacra.
-Dồi dào: Phục hồi toàn bộ Resonance Energy khi vào chiến đấu.
-Bùng nổ: Phục hồi 50 Resonance Energy khi đánh bại kẻ địch.
-Hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Hạng Chiến đấu. Dodge thành công, Dodge Counter và Counterattack tăng đáng kể Hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Hạng Chiến đấu.</t>
+          <t>Mô phỏng: Trong sự kiện Tactical Simulacra, tất cả kẻ địch có 0 Kháng.
+Dồi dào: Hồi phục toàn bộ Năng lượng Cộng hưởng khi vào trận.
+Bùng nổ: Hồi phục 50 Năng lượng Cộng hưởng khi đánh bại kẻ địch.
+Xếp hạng Chiến đấu: Các hành động chiến đấu của bạn sẽ tính vào Xếp hạng Chiến đấu. Né thành công, Phản đòn Né và Phản công sẽ tăng đáng kể Xếp hạng Chiến đấu, trong khi bị đánh trúng sẽ làm giảm mạnh Xếp hạng Chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -24778,7 +24779,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Hoàn thành Độ Khó Nightmare Tái Hiện I</t>
+          <t>Hoàn thành Nightmare Revisits Độ khó I.</t>
         </is>
       </c>
     </row>
@@ -24843,7 +24844,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Hoàn thành Difficulty II - Nightmare Tái Hiện</t>
+          <t>Hoàn thành Nightmare Revisits Độ khó II.</t>
         </is>
       </c>
     </row>
@@ -24908,7 +24909,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Hoàn Thành Difficulty III Cơn Nightmare Lặp Lại</t>
+          <t>Hoàn thành Nightmare Revisits Độ khó III.</t>
         </is>
       </c>
     </row>
@@ -24973,7 +24974,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Hoàn Thành Difficulty IV Cơn Nightmare Lặp Lại</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện Độ Khó IV</t>
         </is>
       </c>
     </row>
@@ -25038,7 +25039,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Hoàn thành Difficulty V của Nightmare Tái Hiện</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện Độ Khó V</t>
         </is>
       </c>
     </row>
@@ -25103,7 +25104,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Hoàn thành Độ Khó Nightmare Tái Hiện VI</t>
+          <t>Hoàn thành Cơn Ác Mộng Tái Hiện Độ Khó VI</t>
         </is>
       </c>
     </row>
@@ -25168,7 +25169,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Đồi Chỉ Huy</t>
+          <t>Lệnh Triệu Hồi</t>
         </is>
       </c>
     </row>
@@ -25234,8 +25235,8 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Hướng đến tòa tháp...
-Hậu duệ Fisalia chỉ để lại bóng dáng rời đi. Anh ta sẽ hoàn thành nhiệm vụ của mình.</t>
+          <t>Đến tháp...
+Hậu duệ của Fisalia chỉ để lại bóng dáng lùi xa. Hắn sẽ hoàn thành nhiệm vụ của mình.</t>
         </is>
       </c>
     </row>
@@ -25300,7 +25301,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Đồi Hoàng Hôn</t>
+          <t>Thăng Bình Hoàng Hôn</t>
         </is>
       </c>
     </row>
@@ -25367,7 +25368,7 @@
       <c r="M379" t="inlineStr">
         <is>
           <t>Khi hoàng hôn buông xuống, vạn vật trở về nhà.
-Có điều gì đó mách bảo bạn rằng một sự hiện diện khó tả đang chờ đợi... mong ngóng những con tàu, con người và mặt trời lặn. Nó đang đợi chờ một thế giới nơi ánh sáng tắt dần và sự im lặng ngự trị. Nó sẽ bước vào bóng tối, nuốt chửng tất cả theo sau.</t>
+Có điều gì đó mách bảo cậu rằng một sự hiện diện khó tả đang chờ đợi… chờ đợi những con tàu, con người và ánh chiều tà. Nó chờ đợi một thế giới nơi ánh sáng tắt lịm và im lặng ngự trị. Nó sẽ bước vào bóng tối, nuốt chửng tất cả.</t>
         </is>
       </c>
     </row>
@@ -25432,7 +25433,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Đồi Tiếng Vang</t>
+          <t>Sự Trỗi Dậy Vang Dội</t>
         </is>
       </c>
     </row>
@@ -25498,7 +25499,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Đàn cá bơi ở đâu? 
+          <t>Đàn cá bơi đi đâu nhỉ? 
 Trên những tòa tháp, vào bầu trời đêm tĩnh lặng...</t>
         </is>
       </c>
@@ -25565,8 +25566,8 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>John Wicktorio, một tín đồ đã nghỉ hưu và là kế toán của Order, phát hiện Echo yêu quý của mình bị sát hại dã man bởi một nhóm côn đồ.
-Quyết tâm đòi lại công bằng và trả thù cho người bạn cũ, ông quay trở lại cuộc chơi để khiến những kẻ thủ ác phải trả giá.</t>
+          <t>John Wicktorio, một tu sĩ đã nghỉ hưu và là kế toán của Hội, phát hiện Echo yêu quý của ông bị bọn côn đồ sát hại dã man.
+Quyết tâm đòi lại công bằng và trả thù cho người bạn cũ, ông đã quay lại cuộc chơi để khiến những kẻ thủ ác phải trả giá.</t>
         </is>
       </c>
     </row>
@@ -25631,7 +25632,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>The Montellis</t>
+          <t>Gia tộc Montelli</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25697,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>"Sao nhà Montelli toàn đặt tên 'Leonardo' vậy? Có quy tắc đặt tên nào mà tôi bỏ lỡ à?"</t>
+          <t>"Sao nhà Montelli toàn đặt tên 'Leonardo' thế? Có quy tắc đặt tên nào mà tao không biết à?"</t>
         </is>
       </c>
     </row>
@@ -25761,7 +25762,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Fiction Của Kẻ Ngốc</t>
+          <t>Ảo Vọng Ngu Ngốc</t>
         </is>
       </c>
     </row>
@@ -25829,10 +25830,10 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>"Cậu không tin được họ lại bôi gì lên pizza thay vì sốt cà chua đâu..."
+          <t>"Cậu không tin được họ lại bôi thứ gì lên bánh pizza thay vì sốt cà chua đâu..."
 "Gì cơ?"
-"Mayonnaise!"
-"Ui, dị giáo quá!"</t>
+"Sốt mayonnaise!"
+"Trời ơi, dị giáo quá!"</t>
         </is>
       </c>
     </row>
@@ -25897,7 +25898,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Once Upon a Time Ở Rinascita</t>
+          <t>Ngày Xửa Ngày Xưa Ở Rinascita</t>
         </is>
       </c>
     </row>
@@ -25962,7 +25963,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>"Chúng ta vượt trên số phận. Chúng ta quyết định ai được hưởng cuộc sống tốt đẹp, và ai phải đối mặt với thử thách khắc nghiệt hơn."</t>
+          <t>"Ta vượt trên số phận. Ta quyết định ai được hưởng cuộc sống tốt đẹp, ai phải chịu đựng nghiệt ngã."</t>
         </is>
       </c>
     </row>
@@ -26027,7 +26028,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>The The Primus</t>
+          <t>Primus</t>
         </is>
       </c>
     </row>
@@ -26092,7 +26093,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>"Fisalias và Montellis có thể lung lay, nhưng Hội không thể."</t>
+          <t>"Dù Fisalias và Montellis có lung lay, Giáo Đoàn vẫn không thể sụp đổ."</t>
         </is>
       </c>
     </row>
@@ -26222,7 +26223,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>"Để trở thành quý tộc đích thực, chỉ có súng thôi chưa đủ. Bạn phải có tầm nhìn."</t>
+          <t>"Để trở thành quý tộc đích thực, chỉ có súng thôi chưa đủ. Ngươi phải có tầm nhìn."</t>
         </is>
       </c>
     </row>
@@ -26352,7 +26353,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>"Điều gì khiến bạn khó chịu nhất ở Ragunna?"</t>
+          <t>"Điều gì khiến cậu khó chịu nhất ở Ragunna?"</t>
         </is>
       </c>
     </row>
@@ -26421,11 +26422,11 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Vụ Nổ Súng ở Nhà Nghỉ
-Buff Mặc Định: Tất cả thành viên trong đội nhận 20 Concerto Energy mỗi 2 giây và không thể bị hạ gục trong thử thách. Sử dụng Intro Skill làm tăng ATK của tất cả thành viên trong đội lên 15%, cộng dồn tối đa 10 lần.
-Buff Chính: Sử dụng Intro Skill triệu hồi Sóng Xung Kích hút kẻ địch vào và gây Havoc DMG bằng 200% ATK của Resonator.
-Buff Nâng Cao: Sóng Xung Kích gây Nổ ngay sau đó, gây Havoc DMG bằng 600% ATK của Resonator.
-Buff Tối Thượng: Đánh bại mục tiêu bằng Sóng Xung Kích hoặc Nổ sẽ phục hồi 20 Concerto Energy cho Resonator.</t>
+          <t>Vụ Nổ Súng Tại Nhà Nghỉ
+Hiệu ứng Mặc Định: Tất cả thành viên trong đội nhận được 20 Concerto Energy mỗi 2 giây và không thể bị hạ gục trong thử thách. Sử dụng Kỹ Năng Khởi Động làm tăng ATK của tất cả thành viên trong đội lên 15%, có thể chồng chất lên đến 10 lần.
+Hiệu ứng Chính: Sử dụng Kỹ Năng Khởi Động triệu hồi Sóng Xung Kích hút kẻ địch vào và gây Sát Thương Havoc bằng 200% ATK của Resonator.
+Hiệu ứng Nâng Cao: Sóng Xung Kích sẽ gây Nổ ngay sau đó, gây Sát Thương Havoc bằng 600% ATK của Resonator.
+Hiệu ứng Tối Thượng: Hạ gục mục tiêu bằng Sóng Xung Kích hoặc Nổ sẽ hồi 20 Concerto Energy cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -26494,11 +26495,11 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Justice to be Served
-Hiệu ứng mặc định: DMG của Basic Attack của tất cả thành viên đội tăng 60% và họ không thể bị hạ gục trong thử thách.
-Hiệu ứng chính: Thực hiện 2 Đòn Phối Hợp hoặc 5 Basic Attack sẽ nhận 1 tầng Tia Chớp. Tầng từ mỗi loại và mỗi Resonator được tính riêng. Khi một trong hai đạt 2 tầng, đòn tấn công sẽ tiêu hao tất cả tầng để triệu hồi 2 Tia Sét đánh trúng mục tiêu, gây Electro DMG bằng 200% ATK của Resonator.
-Hiệu ứng tăng cường: Tia Sét gây thêm Electro DMG bằng 300% ATK của Resonator trong vòng 3 giây sau khi trúng mục tiêu.
-Hiệu ứng tối thượng: Tia Sét kích hoạt Bão Từ, gây Electro DMG bằng 400% ATK của Resonator.</t>
+          <t>Công Lý Sẽ Được Thực Thi
+Tăng cường mặc định: DMG Đòn Basic Attack của tất cả thành viên trong đội tăng 60% và họ không thể bị hạ gục trong thử thách.
+Tăng cường chính: Thực hiện 2 Đòn Phối Hợp hoặc 5 Đòn Basic Attack sẽ nhận được một tầng Tia Lửa Điện. Tầng đếm riêng cho từng loại và từng Resonator. Khi một trong hai đạt 2 tầng, đòn tấn công sẽ tiêu hao toàn bộ tầng đếm để triệu hồi 2 Tia Sét đánh vào mục tiêu, gây Sát Thương Electro bằng 200% ATK của Resonator.
+Tăng cường nâng cao: Trong vòng 3 giây sau khi trúng mục tiêu, Tia Sét gây thêm Sát Thương Electro bằng 300% ATK của Resonator.
+Tăng cường tối thượng: Tia Sét kích hoạt Bão Từ, gây Sát Thương Electro bằng 400% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -26567,11 +26568,11 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Crash and Burn
+          <t>Thiên Đường Cháy Rụi
 Hiệu ứng mặc định: Tất cả thành viên trong đội tăng 50% ATK khi ở trên không và không thể bị hạ gục trong thử thách.
-Hiệu ứng chính: Thực hiện Mid-air Attack sẽ triệu hồi Thiên Thạch, gây Fusion DMG bằng 300% ATK của Resonator. Hiệu ứng này có thể kích hoạt mỗi 3 giây.
-Hiệu ứng tăng cường: Tất cả thành viên trong đội tăng 10% Crit. DMG mỗi giây khi ở trên không, cộng dồn tối đa 10 lần.
-Hiệu ứng tối thượng: Thiên Thạch phát nổ khi trúng mục tiêu, gây Fusion DMG bằng 200% ATK của Resonator và tạo vùng lửa gây Fusion DMG bằng 380% ATK của Resonator.</t>
+Hiệu ứng chính: Khi thực hiện ATK trên không, triệu hồi một Thiên Thạch gây Sát Thương Fusion bằng 300% ATK của Resonator. Hiệu ứng này có thể kích hoạt mỗi 3 giây một lần.
+Hiệu ứng tăng cường: Tất cả thành viên trong đội tăng 10% Crit. DMG mỗi giây khi ở trên không, tối đa 10 lần cộng dồn.
+Hiệu ứng tối thượng: Thiên Thạch phát nổ khi trúng mục tiêu, gây Sát Thương Fusion bằng 200% ATK của Resonator và tạo ra một vùng lửa gây Sát Thương Fusion bằng 380% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -26640,11 +26641,11 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Đập Tan Tất Cả
-Buff Mặc Định: DMG Heavy Attack của tất cả thành viên đội tăng 50% và họ không thể bị hạ gục trong thử thách. Gây DMG bằng Heavy Attack sẽ phục hồi 10 Concerto Energy.
-Buff Chính: Gây DMG bằng Heavy Attack 2 lần sẽ tăng Crit. DMG của Resonator thêm 5% (kích hoạt mỗi 0.1 giây), cộng dồn tối đa 20 lần.
-Buff Nâng Cao: Gây DMG bằng Heavy Attack 5 lần sẽ tạo ra một vụ nổ băng (kích hoạt mỗi 0.1 giây), gây Glacio DMG bằng 400% ATK của Resonator.
-Buff Tối Thượng: Crit. Rate của Heavy Attack tăng 50%.</t>
+          <t>Đập Phăng Tất Cả
+Hiệu ứng Mặc Định: DMG Đòn Heavy Attack của tất cả thành viên đội tăng 50% và họ không thể bị hạ gục trong thử thách. Đánh trúng mục tiêu bằng Đòn Heavy Attack sẽ hồi 10 Concerto Energy.
+Hiệu ứng Chính: Gây DMG Đòn Heavy Attack 2 lần sẽ tăng Crit. DMG của Resonator lên 5% (kích hoạt mỗi 0.1 giây), tối đa 20 lần.
+Hiệu ứng Nâng Cao: Gây DMG Đòn Heavy Attack 5 lần sẽ tạo ra một vụ Nổ Băng (kích hoạt mỗi 0.1 giây), gây DMG Glacio bằng 400% ATK của Resonator.
+Hiệu ứng Tối Thượng: Crit. Rate của Đòn Heavy Attack tăng 50%.</t>
         </is>
       </c>
     </row>
@@ -26713,11 +26714,11 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Quyền Phòng Vệ
-Buff Mặc Định: Dodge thành công triệu hồi một Swirl, gây Aero DMG bằng 300% ATK của Resonator. Tất cả thành viên trong đội không thể bị hạ gục trong thử thách.
-Buff Chính: DMG của Dodge Counter tăng 500%.
-Buff Buff: Đánh trúng kẻ địch bằng Dodge Counter làm tăng Crit. Rate và Crit. DMG của Resonator lên 10%, cộng dồn tối đa 10 lần.
-Buff Tối Thượng: DMG của Dodge Counter tăng 100%. Thực hiện Dodge Counter triệu hồi một Swirl Burst gây Aero DMG bằng 600% ATK của Resonator.</t>
+          <t>Quyền Phòng Vệ Bản Thân
+Hiệu ứng mặc định: Né thành công sẽ triệu hồi một Swirl, gây Sát Thương Aero bằng 300% ATK của Resonator. Tất cả thành viên trong đội không thể bị hạ gục trong thử thách.
+Hiệu ứng chính: Sát Thương Dodge Counter tăng 500%.
+Hiệu ứng nâng cao: Đánh trúng kẻ địch bằng Dodge Counter sẽ tăng Crit. Rate và Crit. DMG của Resonator thêm 10%, có thể cộng dồn tối đa 10 lần.
+Hiệu ứng tối thượng: Sát Thương Dodge Counter tăng 100%. Thực hiện Dodge Counter sẽ triệu hồi một Swirl Burst, gây Sát Thương Aero bằng 600% ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -26786,11 +26787,11 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Thận Trọng Thôi
-Buff Mặc Định: Không nhận sát thương trong 5 giây sẽ tăng Crit. DMG của Resonator thêm 50%, cộng dồn tối đa 5 lần. Mất 1 tầng mỗi khi nhận sát thương.
-Buff Chính: Dodge thành công sẽ tăng ATK của Resonator thêm 20% trong 10 giây, cộng dồn tối đa 10 lần.
-Buff Nâng Cao: Tăng Crit. DMG của tất cả thành viên trong đội thêm 100%. Nhận sát thương sẽ giảm Crit. DMG 100% trong 3 giây.
-Buff Tối Thượng: Attack lại mục tiêu trong vòng 2 giây sau đòn đánh cuối sẽ tăng ATK của Resonator thêm 3% trong 5 giây. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây một lần.</t>
+          <t>Thận Trọng
+Hiệu ứng mặc định: Không nhận DMG trong 5 giây sẽ tăng Crit. DMG của Resonator lên 50%, tối đa 5 tầng. Mỗi lần nhận DMG sẽ mất 1 tầng.
+Hiệu ứng chính: Né thành công sẽ tăng ATK của Resonator lên 20% trong 10 giây, tối đa 10 tầng.
+Hiệu ứng nâng cao: Tăng Crit. DMG của tất cả thành viên trong đội lên 100%. Nhận DMG sẽ giảm Crit. DMG xuống 100% trong 3 giây.
+Hiệu ứng tối thượng: ATK lại mục tiêu trong vòng 2 giây sau đòn đánh trước sẽ tăng ATK của Resonator lên 3% trong 5 giây. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -26855,7 +26856,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Kho tàng lưu giữ bộ sưu tập Echoes và tác phẩm nghệ thuật quý hiếm. Theo nguyên tắc "Bất Khả Xâm Phạm Tài Sản", đây là nơi an toàn và vững chắc nhất ở Rinascita.</t>
+          <t>Kho tàng này lưu giữ bộ sưu tập Echo quý hiếm và tác phẩm nghệ thuật tuyệt đẹp. Tuân theo nguyên tắc "Bất khả xâm phạm tài sản", đây là nơi an toàn và vững chắc nhất ở Rinascita.</t>
         </is>
       </c>
     </row>
@@ -26921,8 +26922,8 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro của Phrolova.
-Giữa không khí cuồng nhiệt, cô mời gọi bạn cùng nhảy múa, đổi lại một câu chuyện và hé lộ sự thật đằng sau bức màn.</t>
+          <t>Sonoro Sphere của Phrolova. 
+Giữa không khí cuồng nhiệt, cô mời gọi ngươi cùng nhảy múa, đổi lại một câu chuyện và vén màn bí mật đằng sau bức màn.</t>
         </is>
       </c>
     </row>
@@ -26988,8 +26989,8 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Một chiếc gương kính màu bí ẩn làm từ tinh thể năng lượng.
-Hãy lại gần. Nhìn vào tôi, dán mắt vào tôi, cho đến khi tâm hồn bạn phơi bày—không phải với "chiếc gương", mà là với tôi.</t>
+          <t>Một tấm gương kính màu bí ẩn làm từ tinh thể năng lượng.
+Lại gần đây. Nhìn vào ta, dán mắt vào ta, cho đến khi linh hồn ngươi phơi bày—không phải trước "tấm gương", mà là trước ta.</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27055,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Cuối mê cung là một hang động kỳ lạ, dường như là nguồn gốc của màn sương mù. Trong bóng tối đặc quánh, những bóng hình méo mó nhấp nháy, kèm theo tiếng gầm gừ trầm thấp đầy bất an...</t>
+          <t>Cuối mê cung là một hang động kỳ lạ, dường như là nguồn gốc của màn sương mù. Trong bóng tối đặc quánh, những bóng ma quái nhấp nháy, kèm theo những tiếng gầm gừ thấp thỏm, khó chịu…</t>
         </is>
       </c>
     </row>
@@ -27119,7 +27120,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Một tổ chức nơi Order niêm phong tất cả các cuốn sách và hồ sơ bị cấm, giờ đây đã bị chìm sâu dưới đáy hồ trong Dark Tide.</t>
+          <t>Nơi Dòng Tu niêm phong tất cả những cuốn sách và hồ sơ cấm, giờ đã chìm sâu dưới đáy hồ trong Đại Triều Tối.</t>
         </is>
       </c>
     </row>
@@ -27184,7 +27185,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Một công trình tôn giáo hai tầng ở Thành phố Ragunna, nơi thờ phụng bức tượng Người Bảo Hộ. Đây cũng là trụ sở của Dòng Trật Tự Vực Sâu.</t>
+          <t>Một công trình tôn giáo hai tầng ở Thành phố Ragunna, dành riêng cho việc thờ phụng bức tượng Sentinel. Đây cũng là trụ sở của Order of the Deep.</t>
         </is>
       </c>
     </row>
@@ -27250,8 +27251,8 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Tần số còn vương lại sau cuộc đọ sức dữ dội giữa hai thế lực hùng mạnh, giờ đây được định hình bởi ký ức của bạn và mang hình hài Lycrosis.
-Người ca sĩ từ cõi bên kia vẫn đang chờ đợi trên sân khấu.</t>
+          <t>Những tần số lưu lại sau cuộc giao tranh khốc liệt giữa hai thế lực hùng mạnh, giờ đây được định hình bởi ký ức của bạn và hiện thân thành Lycrosis.
+Ca sĩ từ cõi bên kia vẫn đang chờ trên sân khấu.</t>
         </is>
       </c>
     </row>
@@ -27316,7 +27317,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro này chứa đựng nguyện vọng của những người đã chìm sâu trong vực thẳm Nỗi Sầu. Trong bóng tối không ngày không đêm, liệu một tia sáng le lói có thể mang đến điều trái tim khao khát?</t>
+          <t>Quả cầu Sonoro này hiện thân cho khát vọng của những kẻ chìm trong vực thẳm Lament. Trong bóng tối không ngày không đêm, liệu một tia sáng le lói có thể mang đến điều trái tim khao khát?</t>
         </is>
       </c>
     </row>
@@ -27381,7 +27382,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Quả Cầu Sonoro này hiện thân cho những ước nguyện của những kẻ chìm đắm trong vực thẳm Lament. Chúng dang rộng đôi cánh thánh thiện, như vòng tay âu yếm của người tình.</t>
+          <t>Quả cầu Sonoro này hiện thân cho khát vọng của những kẻ chìm trong vực thẳm Lament. Họ dang rộng đôi cánh thánh thiện, như vòng tay âu yếm của người tình.</t>
         </is>
       </c>
     </row>
@@ -27446,7 +27447,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Quả cầu Sonoro này thể hiện nguyện vọng của những người đã chìm trong vực Thương Khó. Nó không phải là sự khuất phục trước uy quyền của Order, mà là lời thú nhận nỗi đau của thế giới.</t>
+          <t>Quả cầu Sonoro này hiện thân cho khát vọng của những kẻ chìm trong vực thẳm Lament. Đó không phải sự khuất phục trước uy quyền của Order, mà là lời thú tội cho nỗi đau của thế giới.</t>
         </is>
       </c>
     </row>
@@ -27511,7 +27512,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Quả cầu Sonoro này ghi lại một nghi lễ cổ xưa bị bào mòn bởi Lament. Ở cuối nỗi đau khổ, mong rằng mọi tội lỗi sẽ được tha thứ.</t>
+          <t>Quả cầu Sonoro này ghi lại một nghi lễ cổ xưa bị Lament bào mòn. Khi khổ đau kết thúc, mong mọi tội lỗi đều được tha thứ.</t>
         </is>
       </c>
     </row>
@@ -27576,7 +27577,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Quả cầu Sonoro này ghi lại một nghi lễ cổ xưa bị xói mòn bởi Lament. Bến cảng đã gần kề, tiếng chuông vang lên trong trẻo. Thuyền trưởng ơi, ngài đã nghe thấy tiếng reo hò của dân chúng chưa?</t>
+          <t>Quả cầu Sonoro này ghi lại một nghi lễ cổ xưa bị Lament bào mòn. Bến bờ đã gần, tiếng chuông vang vọng. Hỡi thuyền trưởng, ngài có nghe thấy tiếng reo hò của dân chúng không?</t>
         </is>
       </c>
     </row>
@@ -27641,7 +27642,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Trong thế giới bị Shimmer nuốt chửng, tiếng chuông vẫn ngân vang, nhưng bài học chưa bao giờ đi đến hồi kết. Trong ánh hoàng hôn tàn lụi, một vệt phấn trên bảng đen đột ngột dừng lại. Đây là bài học cuối cùng của Lahai-Roi.</t>
+          <t>Trong thế giới bị Shimmer nuốt chửng, tiếng chuông vẫn vang lên, nhưng bài học chưa bao giờ kết thúc. Dưới ánh hoàng hôn tàn lụi, một vệt phấn đột ngột dừng lại trên bảng đen. Đây là bài học cuối cùng của Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -27706,7 +27707,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Nó tiết lộ những khoảnh khắc cuối cùng của Học viện, nơi Void Storm tràn vào như sương mù đen kịt, nhấn chìm mọi thứ trong đêm tối tĩnh lặng. Trong sự tĩnh lặng chết chóc ấy, Học viện đứng như một minh chứng u ám cho lời tiên tri về các nền văn minh—Mọi thứ đã biết rồi cũng sẽ bị xóa sổ bởi những điều chưa biết.</t>
+          <t>Nó tiết lộ những khoảnh khắc cuối cùng của Học Viện, khi Bão Hư Không tràn vào như sương mù đen đặc, nuốt chửng mọi thứ trong đêm tối tĩnh lặng. Trong sự im lặng chết chóc ấy, Học Viện đứng đó như một minh chứng u ám cho lời tiên tri về các nền văn minh—Mọi thứ đã biết rồi cũng sẽ bị xóa sổ bởi những điều chưa biết.</t>
         </is>
       </c>
     </row>
@@ -27771,7 +27772,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Sau cơn Void Storm, Học viện chỉ còn là đống đổ nát. Những chiếc bàn và dụng cụ trôi nổi như những bóng ma trên dòng thủy triều chết chóc. Sự im lặng ngự trị. Liệu khi nào sẽ có tiếng điểm danh tiếp theo? Có lẽ chẳng còn ai để biết.</t>
+          <t>Sau cơn Bão Hư Không, Học Viện chỉ còn là đống hoang tàn. Những chiếc bàn và dụng cụ trôi lơ lửng như những bóng ma trên dòng thủy triều chết chóc. Im lặng ngự trị. Liệu khi nào sẽ lại vang lên tiếng điểm danh? Có lẽ chẳng còn ai để biết.</t>
         </is>
       </c>
     </row>
@@ -27836,7 +27837,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Mái vòm đã vỡ vụn, và ánh sáng còn sót lại chiếu rọi lên những tàn tích um tùm cỏ dại. Giữa đám cỏ dày đặc, Reactor Drive đang hấp hối chỉ còn giữ lại ký ức mơ hồ về việc nó từng là mặt trời.</t>
+          <t>Mái vòm đã vỡ nát, ánh sáng còn sót lại chiếu lên những tàn tích um tùm cỏ dại. Giữa đám cây hoang, Lò Phản Ứng hấp hối chỉ còn níu giữ ký ức mơ hồ về thời nó từng là mặt trời.</t>
         </is>
       </c>
     </row>
@@ -27901,7 +27902,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Heliogyre, bị Voidmatter làm biến chất, trở thành một lõi năng lượng méo mó giải phóng một tai họa "ánh sáng". Nơi ánh sáng chạm tới, con người và Exoswarm đều bị xóa sổ như thể chưa từng tồn tại.</t>
+          <t>Heliogyre, bị Voidmatter xâm thực, trở thành một lõi năng lượng méo mó, giải phóng thảm họa "ánh sáng". Nơi ánh sáng chạm tới, con người và Exoswarm đều tan biến như chưa từng tồn tại.</t>
         </is>
       </c>
     </row>
@@ -28031,7 +28032,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Đại Kết Cục Đỏ Thẫm</t>
+          <t>Đại Kết Cuộc Đỏ Thẫm</t>
         </is>
       </c>
     </row>
@@ -28226,7 +28227,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Song Bị Giam Cầm</t>
+          <t>Bài Ca Bị Giam Cầm</t>
         </is>
       </c>
     </row>
@@ -28291,7 +28292,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Giáo Đoàn Vực Sâu</t>
+          <t>Lệnh của Vực Sâu</t>
         </is>
       </c>
     </row>
@@ -28356,7 +28357,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Thử Thách Hàng Tuần: Đại Kết Cục Đỏ Thẫm</t>
+          <t>Thử Thách Hàng Tuần: Chung Cục Đẫm Máu</t>
         </is>
       </c>
     </row>
@@ -28421,7 +28422,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Thuốc Cộng Hưởng</t>
+          <t>Thuốc Tăng Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -28486,7 +28487,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Core Năng lượng</t>
+          <t>Lõi Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -28616,7 +28617,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Thuốc Cộng Hưởng</t>
+          <t>Thuốc Tăng Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -28681,7 +28682,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Core Năng lượng</t>
+          <t>Lõi Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -28811,7 +28812,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Làn Gió Thanh Tẩy: Helix</t>
+          <t>Gió Thanh Tẩy: Helix</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28877,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Lời Nguyện Sóng: Cadence Flora</t>
+          <t>Lời Cầu Nguyện Sóng: Cadence Flora</t>
         </is>
       </c>
     </row>
@@ -29006,7 +29007,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Sự Thuần Khiết Vàng: Metallic Drip</t>
+          <t>Thanh Khiết Vàng: Nhuộm Kim</t>
         </is>
       </c>
     </row>
@@ -29071,7 +29072,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Bài Thánh Ca Gió: Waveworn Residue</t>
+          <t>Thánh Ca Gió: Tàn Tích Bị Sóng Xói Mòn</t>
         </is>
       </c>
     </row>
@@ -29201,7 +29202,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Bài Học Hư Không</t>
+          <t>Bài Học Vô Định</t>
         </is>
       </c>
     </row>
@@ -29266,7 +29267,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Bài Học Than Hồng</t>
+          <t>Bài Học Tro Tàn</t>
         </is>
       </c>
     </row>
@@ -29331,7 +29332,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Tàn Tích Bị Lãng Quên</t>
+          <t>Di Vật Bị Lãng Quên</t>
         </is>
       </c>
     </row>
@@ -29462,8 +29463,8 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Kho báu do Gia tộc Montelli kiểm soát chứa đựng bộ sưu tập Echoes và tác phẩm nghệ thuật quý hiếm tuyệt đẹp. Được bao quanh bởi các rào cản tự nhiên và nằm trên vị trí cao, nơi đây mang đến tầm nhìn ngoạn mục của Nimbus Sanctum.
-Bên trong, kho báu có nhiều kho chứa được bảo vệ bởi hàng loạt Echoes Guards và hệ thống an ninh tiên tiến, biến nơi đây thành địa điểm an toàn và bất khả xâm phạm nhất ở Rinascita. Nó thách thức mọi phương thức đột nhập thông thường.</t>
+          <t>Kho tàng do Gia tộc Montelli kiểm soát chứa đựng bộ sưu tập Echo quý hiếm và tác phẩm nghệ thuật tuyệt mỹ. Được bao bọc bởi những bức tường thiên nhiên hùng vĩ và nằm trên địa thế cao, nơi đây mở ra tầm nhìn ngoạn mục về Nimbus Sanctum.
+Bên trong, kho tàng có vô số két sắt được bảo vệ bởi đội quân Echo Guards hùng mạnh cùng hệ thống an ninh tiên tiến, biến nơi này thành pháo đài bất khả xâm phạm nhất ở Rinascita. Không phương pháp đột nhập thông thường nào có thể phá vỡ được.</t>
         </is>
       </c>
     </row>
@@ -29529,8 +29530,8 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Giai đoạn cuối cùng, được xây dựng từ hoa Lycoris, nhuốm đầy nhựa đỏ thẫm thấm vào từng ngóc ngách. Người ca sĩ từ cõi xa xăm đã chờ đợi ở đây từ lâu.
-Hãy cùng cô ấy trong vở kịch bất tận này, và dùng sức mạnh nhỏ bé của bạn để thách thức dòng chảy dữ dội của số phận!</t>
+          <t>Giai đoạn cuối cùng, xây dựng từ những bông Lycoris, nhuốm đỏ thẫm bởi nhựa cây thấm đẫm từng ngóc ngách. Người ca sĩ từ cõi bên kia đã chờ đợi ở đây từ lâu.
+Hãy cùng nàng tham gia vở diễn bất tận này, và dùng sức mạnh nhỏ bé của ngươi để thách thức dòng chảy cuồng nộ của số phận!</t>
         </is>
       </c>
     </row>
@@ -29595,7 +29596,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Phía sau tấm gương là một cõi nơi ảo ảnh quá khứ hòa quyện với hiện thực, nhưng con đường phía trước lại dẫn đến một định mệnh hoàn toàn khác. Bước về phía ánh sáng để đón nhận sự hoàn hảo đã chờ đợi từ lâu... hoặc ngắm bắn vào nó.</t>
+          <t>Phía sau tấm gương là một cõi nơi ảo ảnh quá khứ hòa quyện với hiện thực, nhưng con đường phía trước lại dẫn đến một vận mệnh hoàn toàn khác. Bước về phía ánh sáng để đón nhận sự hoàn hảo đã chờ đợi từ lâu... hoặc chĩa súng vào nó.</t>
         </is>
       </c>
     </row>
@@ -29660,7 +29661,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Cuối mê cung là một hang động kỳ lạ, dường như là nguồn gốc của màn sương mù. Trong bóng tối đặc quánh, những bóng hình méo mó nhấp nháy, kèm theo tiếng gầm gừ trầm thấp đầy bất an...</t>
+          <t>Cuối mê cung là một hang động kỳ lạ, dường như là nguồn gốc của màn sương mù. Trong bóng tối đặc quánh, những bóng ma quái nhấp nháy, kèm theo những tiếng gầm gừ thấp thỏm, khó chịu…</t>
         </is>
       </c>
     </row>
@@ -29725,7 +29726,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Nhà tù xây bằng quyền lực và nỗi sợ có thể xiềng xích tâm trí—nhưng không thể bịt miệng bài ca trỗi dậy từ trái tim. Cũng như sa mạc cằn cỗi không thể vùi lấp dòng suối sự sống, và đêm tối nhất không thể dập tắt ánh sao.</t>
+          <t>Nhà tù xây bằng quyền lực và nỗi sợ có thể trói buộc tâm trí—nhưng không thể bịt miệng khúc ca trỗi dậy từ trái tim. Cũng như sa mạc cằn cỗi không thể vùi lấp dòng suối sự sống, và đêm tối tăm nhất không thể dập tắt ánh sao.</t>
         </is>
       </c>
     </row>
@@ -29791,8 +29792,8 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Một công trình linh thiêng hai tầng ở Thành phố Ragunna, dành để thờ phụng bức tượng Sentinel. Đây cũng là trụ sở của Order of the Deep.
-Nhà nguyện nước tầng trên kết nối với biển chảy qua Thành phố Ragunna, nước lên xuống theo thủy triều như thể đang thở cùng nhịp với Sentinel. Vì vậy, nơi đây được gọi là Tidal Sanctuary.</t>
+          <t>Một công trình tôn giáo hai tầng ở Thành phố Ragunna, dành riêng cho việc thờ phụng bức tượng Sentinel. Đây cũng là trụ sở của Order of the Deep.
+Nhà nguyện nước tầng trên nối liền với dòng biển chảy qua Thành phố Ragunna, nước lên xuống theo thủy triều như thể đang thở cùng nhịp với Sentinel. Vì thế, nơi đây được gọi là Thánh Đường Thủy Triều.</t>
         </is>
       </c>
     </row>
@@ -29858,8 +29859,8 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Âm nhạc vẫn tiếp tục, và tấm màn đỏ lại một lần nữa được kéo lên.
-Liệu cậu có muốn cùng nàng nhảy tiếp trong vở kịch bất tận này?</t>
+          <t>Âm nhạc vẫn tiếp tục, bức màn đỏ lại được kéo lên.
+Trong vở kịch bất tận này, ngươi có muốn cùng nàng nhảy thêm một điệu không?</t>
         </is>
       </c>
     </row>
@@ -29924,7 +29925,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Vượt qua thử thách của Sonoro Sphere để nhận vật phẩm tăng cường Resonator.</t>
+          <t>Vượt qua thử thách của Tổ Tacet này để nhận vật phẩm tăng cường Resonator.</t>
         </is>
       </c>
     </row>
@@ -29989,7 +29990,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Vượt qua thử thách của Sonoro Sphere để nhận vật phẩm tăng cường Weapon.</t>
+          <t>Vượt qua thử thách của Tổ Tacet này để nhận vật phẩm tăng cường Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -30054,7 +30055,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Vượt qua thử thách của Sonoro Sphere này để nhận được tài nguyên thiết yếu.</t>
+          <t>Vượt qua thử thách của Tổ Tacet này để nhận những tài nguyên không thể thiếu.</t>
         </is>
       </c>
     </row>
@@ -30119,7 +30120,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Vượt qua thử thách của Sonoro Sphere để nhận vật phẩm tăng cường Resonator.</t>
+          <t>Vượt qua thử thách của Tổ Tacet này để nhận vật phẩm tăng cường Resonator.</t>
         </is>
       </c>
     </row>
@@ -30184,7 +30185,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Vượt qua thử thách của Sonoro Sphere để nhận vật phẩm tăng cường Weapon.</t>
+          <t>Vượt qua thử thách của Tổ Tacet này để nhận vật phẩm tăng cường Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -30249,7 +30250,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Vượt qua thử thách của Sonoro Sphere này để nhận được tài nguyên thiết yếu.</t>
+          <t>Vượt qua thử thách của Tổ Tacet này để nhận những tài nguyên không thể thiếu.</t>
         </is>
       </c>
     </row>
@@ -30314,7 +30315,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Trong Sonoro Sphere này, sinh ra từ biển cả bị tàn phá bởi tai họa, chứa đựng các vật phẩm tăng cường Resonator và Weapon mang hiệu ứng Waveworn.</t>
+          <t>Trong Sonoro Sphere này, sinh ra từ biển cả bị tàn phá bởi tai họa, chứa đựng những vật phẩm tăng cường Resonator và Vũ Khí mang hiệu ứng Waveworn.</t>
         </is>
       </c>
     </row>
@@ -30379,7 +30380,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Trong Sonoro Sphere này, sinh ra từ biển cả bị tàn phá bởi tai họa, chứa đựng các vật phẩm tăng cường Resonator và Weapon mang hiệu ứng Waveworn.</t>
+          <t>Trong Sonoro Sphere này, sinh ra từ biển cả bị tàn phá bởi tai họa, chứa đựng những vật phẩm tăng cường Resonator và Vũ Khí mang hiệu ứng Waveworn.</t>
         </is>
       </c>
     </row>
@@ -30444,7 +30445,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Trong Sonoro Sphere này, sinh ra từ biển cả bị tàn phá bởi tai họa, chứa đựng các vật phẩm tăng cường Resonator và Weapon mang hiệu ứng Waveworn.</t>
+          <t>Trong Sonoro Sphere này, sinh ra từ biển cả bị tàn phá bởi tai họa, chứa đựng những vật phẩm tăng cường Resonator và Vũ Khí mang hiệu ứng Waveworn.</t>
         </is>
       </c>
     </row>
@@ -30509,7 +30510,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Trong Sonoro Sphere này, sinh ra từ biển cả bị tàn phá bởi tai họa, chứa đựng các vật phẩm tăng cường Resonator và Weapon mang hiệu ứng Waveworn.</t>
+          <t>Trong Sonoro Sphere này, sinh ra từ biển cả bị tàn phá bởi tai họa, chứa đựng những vật phẩm tăng cường Resonator và Vũ Khí mang hiệu ứng Waveworn.</t>
         </is>
       </c>
     </row>
@@ -30574,7 +30575,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Trong Sonoro Sphere này, sinh ra từ biển cả bị tàn phá bởi tai họa, chứa đựng các vật phẩm tăng cường Resonator và Weapon mang hiệu ứng Waveworn.</t>
+          <t>Trong Sonoro Sphere này, sinh ra từ biển cả bị tàn phá bởi tai họa, chứa đựng những vật phẩm tăng cường Resonator và Vũ Khí mang hiệu ứng Waveworn.</t>
         </is>
       </c>
     </row>
@@ -30639,7 +30640,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Trong thế giới bị Shimmer nuốt chửng, tiếng chuông vẫn ngân vang, nhưng bài học chưa bao giờ đi đến hồi kết. Trong ánh hoàng hôn tàn lụi, một vệt phấn trên bảng đen đột ngột dừng lại. Đây là bài học cuối cùng của Lahai-Roi.</t>
+          <t>Trong thế giới bị Shimmer nuốt chửng, tiếng chuông vẫn vang lên, nhưng bài học chưa bao giờ kết thúc. Dưới ánh hoàng hôn tàn lụi, một vệt phấn đột ngột dừng lại trên bảng đen. Đây là bài học cuối cùng của Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -30704,7 +30705,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Nó tiết lộ những khoảnh khắc cuối cùng của Học viện, nơi Void Storm tràn vào như sương mù đen kịt, nhấn chìm mọi thứ trong đêm tối tĩnh lặng. Trong sự tĩnh lặng chết chóc ấy, Học viện đứng như một minh chứng u ám cho lời tiên tri về các nền văn minh—Mọi thứ đã biết rồi cũng sẽ bị xóa sổ bởi những điều chưa biết.</t>
+          <t>Nó tiết lộ những khoảnh khắc cuối cùng của Học Viện, khi Bão Hư Không tràn vào như sương mù đen đặc, nuốt chửng mọi thứ trong đêm tối tĩnh lặng. Trong sự im lặng chết chóc ấy, Học Viện đứng đó như một minh chứng u ám cho lời tiên tri về các nền văn minh—Mọi thứ đã biết rồi cũng sẽ bị xóa sổ bởi những điều chưa biết.</t>
         </is>
       </c>
     </row>
@@ -30769,7 +30770,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Sau cơn Void Storm, Học viện chỉ còn là đống đổ nát. Những chiếc bàn và dụng cụ trôi nổi như những bóng ma trên dòng thủy triều chết chóc. Sự im lặng ngự trị. Liệu khi nào sẽ có tiếng điểm danh tiếp theo? Có lẽ chẳng còn ai để biết.</t>
+          <t>Sau cơn Bão Hư Không, Học Viện chỉ còn là đống hoang tàn. Những chiếc bàn và dụng cụ trôi lơ lửng như những bóng ma trên dòng thủy triều chết chóc. Im lặng ngự trị. Liệu khi nào sẽ lại vang lên tiếng điểm danh? Có lẽ chẳng còn ai để biết.</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30835,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Mái vòm đã vỡ vụn, và ánh sáng còn sót lại chiếu rọi lên những tàn tích um tùm cỏ dại. Giữa đám cỏ dày đặc, Reactor Drive đang hấp hối chỉ còn giữ lại ký ức mơ hồ về việc nó từng là mặt trời.</t>
+          <t>Mái vòm đã vỡ nát, ánh sáng còn sót lại chiếu lên những tàn tích um tùm cỏ dại. Giữa đám cây hoang, Lò Phản Ứng hấp hối chỉ còn níu giữ ký ức mơ hồ về thời nó từng là mặt trời.</t>
         </is>
       </c>
     </row>
@@ -30899,7 +30900,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Heliogyre, bị Voidmatter làm biến chất, trở thành một lõi năng lượng méo mó giải phóng một tai họa "ánh sáng". Nơi ánh sáng chạm tới, con người và Exoswarm đều bị xóa sổ như thể chưa từng tồn tại.</t>
+          <t>Heliogyre, bị Voidmatter xâm thực, trở thành một lõi năng lượng méo mó, giải phóng thảm họa "ánh sáng". Nơi ánh sáng chạm tới, con người và Exoswarm đều tan biến như chưa từng tồn tại.</t>
         </is>
       </c>
     </row>
@@ -31029,7 +31030,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Phòng Trưng bày Hiệp hội Trị liệu Tâm lý Ngưỡng Tâm lý Thay thế (hay còn gọi là Hiệp hội Trị liệu Tâm lý)</t>
+          <t>Phòng Trưng bày Hiệp hội Trị liệu Tâm lý Ngưỡng (hay còn gọi là Hiệp hội Trị liệu Tâm lý)</t>
         </is>
       </c>
     </row>
@@ -31094,7 +31095,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>&lt;color=Wind&gt;Aero DMG Bonus&lt;/color&gt; 40%.</t>
+          <t>Tỷ lệ &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; tăng thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -31159,7 +31160,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>&lt;color=Light&gt;Spectro DMG&lt;/color&gt; tăng 40%.</t>
+          <t>Tăng &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -31224,7 +31225,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>&lt;color=Dark&gt;Havoc DMG&lt;/color&gt; tăng 40%.</t>
+          <t>&lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; tăng thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -31289,7 +31290,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Gây Tune Break DMG sẽ tăng Crit. DMG cho tất cả Resonators trong đội thêm 40% trong 10 giây.</t>
+          <t>Gây Sát Thương Đột Phá Giai Điệu sẽ tăng Crit. DMG cho tất cả Resonator trong đội lên 40% trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -31354,7 +31355,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Gây DMG Break Nhịp làm tăng ATK 40% cho tất cả Resonators trong đội trong 10 giây.</t>
+          <t>Gây Sát Thương Phá Nhịp sẽ tăng ATK 40% cho tất cả Resonator trong đội trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -31419,7 +31420,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Gây Tune Break DMG làm tăng DMG toàn thuộc tính lên 40% cho tất cả Resonators trong đội trong 10 giây.</t>
+          <t>Gây Sát Thương Phá Nhịp sẽ tăng Sát Thương Thuộc Tính 40% cho tất cả Resonator trong đội trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -31484,7 +31485,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Gây Tune Break DMG làm tăng Heavy Attack DMG của tất cả Resonators trong đội lên 40% trong 10 giây.</t>
+          <t>Gây Sát Thương Đột Phá Giai Điệu sẽ tăng Sát Thương Đòn Heavy Attack cho tất cả Resonator trong đội lên 40% trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -31549,7 +31550,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Gây DMG Phá Nhịp sẽ tăng DMG của Basic Attack lên 40% cho tất cả Resonators trong đội trong 10 giây.</t>
+          <t>Gây Sát Thương Phá Nhịp sẽ tăng Sát Thương Đòn Cơ Bản 40% cho tất cả Resonator trong đội trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -31614,7 +31615,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Gây DMG Phá Nhịp tăng DMG Resonance Skill của tất cả Resonators trong đội lên 40% trong 10 giây.</t>
+          <t>Gây Sát Thương Đột Phá Giai Điệu sẽ tăng Sát Thương Kỹ Năng Dư Âm cho tất cả Resonator trong đội lên 40% trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -31679,7 +31680,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Gây Tune Break DMG sẽ tăng Resonance Liberation DMG thêm 40% cho tất cả Resonators trong đội trong 10 giây.</t>
+          <t>Gây Sát Thương Đột Phá Giai Điệu sẽ tăng Sát Thương Resonance Liberation cho tất cả Resonator trong đội lên 40% trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -31744,7 +31745,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Gây DMG Break Nhạc sẽ tăng DMG Resonance Skill của tất cả Resonators trong đội lên 40% trong 10 giây.</t>
+          <t>Gây Sát Thương Đột Phá Giai Điệu sẽ tăng Sát Thương Resonance Skill cho tất cả Resonator trong đội lên 40% trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -31809,7 +31810,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Tăng 66% DMG Resonance Skill.</t>
+          <t>Sát Thương Resonance Skill tăng 66%.</t>
         </is>
       </c>
     </row>
@@ -31874,7 +31875,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>DMG Heavy Attack tăng 66%.</t>
+          <t>Sát Thương Đòn Heavy Attack tăng thêm 66%.</t>
         </is>
       </c>
     </row>
@@ -31939,7 +31940,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>DMG của Resonance Liberation tăng 66%.</t>
+          <t>DMG Resonance Liberation tăng 66%.</t>
         </is>
       </c>
     </row>
@@ -32004,7 +32005,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>DMG của Basic Attack tăng 66%.</t>
+          <t>DMG Basic Attack tăng 66%</t>
         </is>
       </c>
     </row>
@@ -32069,7 +32070,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>&lt;color=Ice&gt;Glacio DMG&lt;/color&gt; tăng 40%.</t>
+          <t>Tăng &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32138,10 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, Resonance Energy được phục hồi 50% và RES với Tất cả Attributes của mục tiêu giảm xuống 0. Kích hoạt Phản Đòn sẽ giảm Vibration Strength của mục tiêu đi 21,5%. Các hành động chiến đấu của bạn sẽ được tính vào Combat Rank. Đánh bại mục tiêu sẽ tăng đáng kể Combat Rank của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các debuff sau dựa trên Combat Rank của bạn:</t>
+          <t>Khi thử thách bắt đầu, Resonance Energy sẽ hồi phục 50%, và Kháng Tất Cả Thuộc Tính của mục tiêu giảm xuống 0. Kích hoạt Phản Công sẽ làm giảm Sức Mạnh Rung Động của mục tiêu đi 21.5%. Các hành động chiến đấu của bạn sẽ tính vào Xếp Hạng Chiến Đấu. Đánh bại mục tiêu sẽ tăng đáng kể Xếp Hạng Chiến Đấu của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các hiệu ứng suy yếu sau dựa trên Xếp Hạng Chiến Đấu của bạn:
+A: Mục tiêu chịu thêm 50% sát thương.
+S: Mục tiêu chịu thêm 100% sát thương.
+SS: Mục tiêu chịu thêm 200% sát thương.</t>
         </is>
       </c>
     </row>
@@ -32205,7 +32209,10 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, Resonance Energy được phục hồi 50% và RES với Tất cả Attributes của mục tiêu giảm xuống 0. Kích hoạt Phản Đòn sẽ giảm Vibration Strength của mục tiêu đi 21,5%. Các hành động chiến đấu của bạn sẽ được tính vào Combat Rank. Đánh bại mục tiêu sẽ tăng đáng kể Combat Rank của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các debuff sau dựa trên Combat Rank của bạn:</t>
+          <t>Khi thử thách bắt đầu, Resonance Energy sẽ hồi phục 50%, và Kháng Tất Cả Thuộc Tính của mục tiêu giảm xuống 0. Kích hoạt Phản Công sẽ làm giảm Sức Mạnh Rung Động của mục tiêu đi 21.5%. Các hành động chiến đấu của bạn sẽ tính vào Xếp Hạng Chiến Đấu. Đánh bại mục tiêu sẽ tăng đáng kể Xếp Hạng Chiến Đấu của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các hiệu ứng suy yếu sau dựa trên Xếp Hạng Chiến Đấu của bạn:
+A: Mục tiêu chịu thêm 50% sát thương.
+S: Mục tiêu chịu thêm 100% sát thương.
+SS: Mục tiêu chịu thêm 200% sát thương.</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32280,10 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, Resonance Energy được phục hồi 50% và RES với Tất cả Attributes của mục tiêu giảm xuống 0. Kích hoạt Phản Đòn sẽ giảm Vibration Strength của mục tiêu đi 21,5%. Các hành động chiến đấu của bạn sẽ được tính vào Combat Rank. Đánh bại mục tiêu sẽ tăng đáng kể Combat Rank của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các debuff sau dựa trên Combat Rank của bạn:</t>
+          <t>Khi thử thách bắt đầu, Resonance Energy sẽ hồi phục 50%, và Kháng Tất Cả Thuộc Tính của mục tiêu giảm xuống 0. Kích hoạt Phản Công sẽ làm giảm Sức Mạnh Rung Động của mục tiêu đi 21.5%. Các hành động chiến đấu của bạn sẽ tính vào Xếp Hạng Chiến Đấu. Đánh bại mục tiêu sẽ tăng đáng kể Xếp Hạng Chiến Đấu của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các hiệu ứng suy yếu sau dựa trên Xếp Hạng Chiến Đấu của bạn:
+A: Mục tiêu chịu thêm 50% sát thương.
+S: Mục tiêu chịu thêm 100% sát thương.
+SS: Mục tiêu chịu thêm 200% sát thương.</t>
         </is>
       </c>
     </row>
@@ -32341,7 +32351,10 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, Resonance Energy được phục hồi 50% và RES với Tất cả Attributes của mục tiêu giảm xuống 0. Kích hoạt Phản Đòn sẽ giảm Vibration Strength của mục tiêu đi 21,5%. Các hành động chiến đấu của bạn sẽ được tính vào Combat Rank. Đánh bại mục tiêu sẽ tăng đáng kể Combat Rank của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các debuff sau dựa trên Combat Rank của bạn:</t>
+          <t>Khi thử thách bắt đầu, Resonance Energy sẽ hồi phục 50%, và Kháng Tất Cả Thuộc Tính của mục tiêu giảm xuống 0. Kích hoạt Phản Công sẽ làm giảm Sức Mạnh Rung Động của mục tiêu đi 21.5%. Các hành động chiến đấu của bạn sẽ tính vào Xếp Hạng Chiến Đấu. Đánh bại mục tiêu sẽ tăng đáng kể Xếp Hạng Chiến Đấu của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các hiệu ứng suy yếu sau dựa trên Xếp Hạng Chiến Đấu của bạn:
+A: Mục tiêu chịu thêm 50% sát thương.
+S: Mục tiêu chịu thêm 100% sát thương.
+SS: Mục tiêu chịu thêm 200% sát thương.</t>
         </is>
       </c>
     </row>
@@ -32409,7 +32422,10 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, Resonance Energy được phục hồi 50% và RES với Tất cả Attributes của mục tiêu giảm xuống 0. Kích hoạt Phản Đòn sẽ giảm Vibration Strength của mục tiêu đi 21,5%. Các hành động chiến đấu của bạn sẽ được tính vào Combat Rank. Đánh bại mục tiêu sẽ tăng đáng kể Combat Rank của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các debuff sau dựa trên Combat Rank của bạn:</t>
+          <t>Khi thử thách bắt đầu, Resonance Energy sẽ hồi phục 50%, và Kháng Tất Cả Thuộc Tính của mục tiêu giảm xuống 0. Kích hoạt Phản Công sẽ làm giảm Sức Mạnh Rung Động của mục tiêu đi 21.5%. Các hành động chiến đấu của bạn sẽ tính vào Xếp Hạng Chiến Đấu. Đánh bại mục tiêu sẽ tăng đáng kể Xếp Hạng Chiến Đấu của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các hiệu ứng suy yếu sau dựa trên Xếp Hạng Chiến Đấu của bạn:
+A: Mục tiêu chịu thêm 50% sát thương.
+S: Mục tiêu chịu thêm 100% sát thương.
+SS: Mục tiêu chịu thêm 200% sát thương.</t>
         </is>
       </c>
     </row>
@@ -32477,7 +32493,10 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, Resonance Energy được phục hồi 50% và RES với Tất cả Attributes của mục tiêu giảm xuống 0. Kích hoạt Phản Đòn sẽ giảm Vibration Strength của mục tiêu đi 21,5%. Các hành động chiến đấu của bạn sẽ được tính vào Combat Rank. Đánh bại mục tiêu sẽ tăng đáng kể Combat Rank của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các debuff sau dựa trên Combat Rank của bạn:</t>
+          <t>Khi thử thách bắt đầu, Resonance Energy sẽ hồi phục 50%, và Kháng Tất Cả Thuộc Tính của mục tiêu giảm xuống 0. Kích hoạt Phản Công sẽ làm giảm Sức Mạnh Rung Động của mục tiêu đi 21.5%. Các hành động chiến đấu của bạn sẽ tính vào Xếp Hạng Chiến Đấu. Đánh bại mục tiêu sẽ tăng đáng kể Xếp Hạng Chiến Đấu của bạn. Khi mục tiêu bị bất động, chúng sẽ nhận một trong các hiệu ứng suy yếu sau dựa trên Xếp Hạng Chiến Đấu của bạn:
+A: Mục tiêu chịu thêm 50% sát thương.
+S: Mục tiêu chịu thêm 100% sát thương.
+SS: Mục tiêu chịu thêm 200% sát thương.</t>
         </is>
       </c>
     </row>
@@ -32542,7 +32561,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>End Của Kẻ Ăn Năn I</t>
+          <t>Kết Cục Của Kẻ Ăn Năn I</t>
         </is>
       </c>
     </row>
@@ -32607,7 +32626,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Kết Cục Sám Hối II</t>
+          <t>Kết Cục Của Kẻ Ăn Năn II</t>
         </is>
       </c>
     </row>
@@ -32672,7 +32691,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Kết Cục Sám Hối III</t>
+          <t>Hồi Kết của Kẻ Ăn Năn III</t>
         </is>
       </c>
     </row>
@@ -32737,7 +32756,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Kết Cục Sám Hối IV</t>
+          <t>Hồi Kết của Kẻ Ăn Năn IV</t>
         </is>
       </c>
     </row>
@@ -32802,7 +32821,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Kết Cục Sám Hối V</t>
+          <t>Hồi Kết của Kẻ Ăn Năn V</t>
         </is>
       </c>
     </row>
@@ -32881,21 +32900,21 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>[Giới thiệu]
-Sau một thập kỷ chờ đợi, Carnevale được mong đợi từ lâu đã thổi bùng ngọn lửa đam mê không ngừng tắt.
-Thành phố Nước vừa hé lộ một góc bí mật. Đây chính là thời điểm tốt nhất để căng buồm, lướt theo gió và khám phá những ngóc ngách chưa ai đặt chân đến của vùng đất bí ẩn này.
-Khi bức màn thế giới được vén lên, một cuộc thám hiểm mới đang gọi tên—còn chờ gì nữa? Hãy bắt đầu phiêu lưu ngay!
-[Điều kiện tham gia]
-Đạt Cấp Liên Minh 22 và mở khóa Công Cụ: Bay Lượn.
-[Quy tắc sự kiện]
-1. Trong sự kiện, bạn có thể mời người chơi khác tham gia Overdash Challenge ở Chế độ Hợp tác. Người về đích đầu tiên sẽ thắng.
-2. Khi người chơi đầu tiên hoàn thành, thử thách sẽ bước vào giai đoạn nước rút 20 giây. Sau khi giai đoạn này kết thúc, kết quả sẽ được chốt.
-3. Chiến đấu bị vô hiệu hóa trong thử thách. Người chơi phải đi theo chỉ dẫn để hoàn thành.
-4. Points cuối gồm hai phần: Points Hoàn thành Đường đua và Points Ranking:
-I. Points Hoàn thành Đường đua được tính khi đến các điểm kiểm tra trên đường đua.
-II. Points Ranking được tính dựa trên thứ tự về đích của người chơi.
-[Lưu ý]
-Resonators có chiều cao khác nhau sẽ chạy với tốc độ khác nhau.</t>
+          <t>Về sự kiện
+Sau một thập kỷ chờ đợi, Carnevale huyền thoại cuối cùng đã trở lại, thổi bùng ngọn lửa đam mê không ngừng tắt.
+Thành phố Nước vừa hé lộ một góc bí ẩn của mình. Đây chính là thời điểm hoàn hảo để căng buồm, lướt theo gió và khám phá những góc khuất chưa ai đặt chân tới của vùng đất kỳ bí này.
+Khi bức màn thế giới dần được vén lên, một cuộc phiêu lưu mới đang chờ đón—còn chần chừ gì nữa? Hãy bắt đầu ngay thôi!
+Điều kiện tham gia
+Đạt Cấp Liên Minh 22 và mở khóa Tiện ích: Bay.
+Quy tắc sự kiện
+1. Trong sự kiện, bạn có thể mời người chơi khác tham gia Thử thách Overdash ở Chế độ Hợp tác. Ai về đích trước sẽ là người chiến thắng.
+2. Khi người chơi đầu tiên về đích, thử thách sẽ bước vào giai đoạn nước rút 20 giây. Sau khi giai đoạn này kết thúc, kết quả sẽ được xác định.
+3. Chiến đấu bị vô hiệu hóa trong thử thách. Người chơi phải đi theo các điểm đánh dấu để hoàn thành thử thách.
+4. Điểm cuối cùng bao gồm hai phần: Điểm Hoàn Thành Đường Đua và Điểm Xếp Hạng:
+I. Điểm Hoàn Thành Đường Đua được tính khi đến các điểm kiểm tra đã chỉ định trên đường đua.
+II. Điểm Xếp Hạng được tính dựa trên thứ tự về đích của người chơi.
+Lưu ý
+Resonator ở các độ cao khác nhau sẽ có tốc độ di chuyển khác nhau.</t>
         </is>
       </c>
     </row>
@@ -32961,8 +32980,8 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Một cỗ máy chiến đấu chính xác và mạnh mẽ được cải tiến bằng công nghệ đặc biệt. Nó thực hiện mệnh lệnh của chủ nhân với lòng trung thành tuyệt đối.
-Mọi dấu vết về hình dạng ban đầu của nó đều đã phai mờ, chỉ còn lại bản năng chiến đấu được mài giũa tinh vi trong tần số của nó. Là một người bảo vệ kiên cường, nó thích nghi hoàn hảo với mọi loại hình chiến đấu. Khi cần thiết, nó kích hoạt một bộ phận đặc biệt để tăng cường khả năng di chuyển hoặc giải phóng toàn bộ năng lượng trong một vụ nổ hủy diệt.</t>
+          <t>Một cỗ máy chiến đấu chính xác và mạnh mẽ, được nâng cấp bằng công nghệ đặc biệt. Nó thực hiện mệnh lệnh của chủ nhân với lòng trung thành tuyệt đối.
+Mọi dấu vết về hình dáng ban đầu đã phai mờ, chỉ còn lại bản năng chiến đấu sắc bén trong tần số của nó. Là một người bảo vệ bất khuất, nó thích nghi hoàn hảo với mọi loại hình chiến đấu. Khi cần, nó kích hoạt một bộ phận đặc biệt để tăng cường khả năng di chuyển hoặc giải phóng toàn bộ năng lượng trong một đòn tấn công hủy diệt.</t>
         </is>
       </c>
     </row>
@@ -33028,8 +33047,8 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Từng là một sinh vật còn sót lại trong Nimbus Sanctum, Lorelei đã có được trí tuệ nhờ sức mạnh của Sentinel Imperator, được giao nhiệm vụ thanh tẩy những tần số bị tha hóa trôi dạt trong mây.
-Tuy nhiên, những ham muốn xấu xa đã biến nàng thành "Nữ hoàng Night tối", khao khát che phủ Sanctum trong bóng tối vĩnh cửu để xóa sạch mọi tội lỗi. Với chút lý trí còn sót lại, Lorelei đã tự phong ấn mình trong đại sảnh, nơi nàng cất lên khúc bi ca ám ảnh, chờ đợi người có thể đánh thức mình khỏi giấc ngủ u tối này.</t>
+          <t>Từng là một sinh vật còn sót lại trong Nimbus Sanctum, Lorelei đã có được trí tuệ nhờ sức mạnh của Sentinel Imperator, được giao trọng trách thanh tẩy những tần số nhiễm độc trôi nổi trên mây.
+Nhưng dục vọng đen tối đã biến nàng thành "Nữ Hoàng Bóng Đêm", khao khát bao phủ Sanctum trong bóng tối vĩnh cửu để xóa sạch mọi tội lỗi. Với chút lý trí cuối cùng, Lorelei đã tự phong ấn mình trong đại sảnh, nơi nàng cất lên khúc bi ca u ám, chờ đợi người có thể đánh thức mình khỏi giấc ngủ thê lương này.</t>
         </is>
       </c>
     </row>
@@ -33096,9 +33115,9 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Một loài chim săn mồi đậu tại Bãi Than Vãn Aix, tiếng kêu như một bài ca ai oán.
-Truyền thuyết kể rằng loài chim này từng có một người bạn đời và tiếng hót của chúng là một âm thanh tuyệt đẹp. Tên của chúng không được lưu truyền, nhưng những bản thánh ca của chúng đã được con người ghi chép và bảo tồn.
-Cho đến khi một trong hai con qua đời. Con còn lại khóc suốt ngày, tiếng kêu bi thương đến mức được gọi là Chim Than Vãn Aix.</t>
+          <t>Một loài động vật giống chim săn mồi đậu tại Đầm Than Vãn Aix, với tiếng kêu như một bản nhạc buồn.
+Truyền thuyết kể rằng loài chim này từng có một người bạn đời, và tiếng hót của chúng là một âm thanh tuyệt đẹp. Tên của chúng không được lưu truyền, nhưng những khúc ca của chúng đã được con người ghi lại và bảo tồn.
+Cho đến khi một trong hai con qua đời. Con còn lại khóc suốt ngày, tiếng kêu thảm thiết đến mức được gọi là Chim Than Vãn Aix.</t>
         </is>
       </c>
     </row>
@@ -33166,10 +33185,10 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Trong thử thách này: 
-&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của Roccia không có Cooldown.
-Chi phí STA khi bay được giảm.
-Hiệu ứng chính: &lt;color=Highlight&gt;Đánh Đâm và Đòn Lao Dốc&lt;/color&gt; triệu hồi Xoáy Nham gây Havoc DMG.</t>
+          <t>Trong thử thách này:
+&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của &lt;color=Highlight&gt;Roccia&lt;/color&gt; không có thời gian hồi chiêu.
+Chi phí STA khi bay giảm.
+Tăng cường chính: &lt;color=Highlight&gt;Lao và Tấn Công Hạ Bay&lt;/color&gt; sẽ triệu hồi Lốc Xoáy gây DMG Havoc.</t>
         </is>
       </c>
     </row>
@@ -33238,9 +33257,9 @@
       <c r="M498" t="inlineStr">
         <is>
           <t>Trong thử thách này:
-&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của Roccia không có Cooldown.
-Chi phí STA khi bay được giảm.
-Buff chính: &lt;color=Highlight&gt;Đòn Dash và Plunge Attack&lt;/color&gt; triệu hồi Cyclone gây Havoc DMG.</t>
+&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của &lt;color=Highlight&gt;Roccia&lt;/color&gt; không có thời gian hồi chiêu.
+Chi phí STA khi bay giảm.
+Tăng cường chính: &lt;color=Highlight&gt;Lao và Tấn Công Hạ Bay&lt;/color&gt; sẽ triệu hồi Lốc Xoáy gây DMG Havoc.</t>
         </is>
       </c>
     </row>
@@ -33309,9 +33328,9 @@
       <c r="M499" t="inlineStr">
         <is>
           <t>Trong thử thách này:
-&lt;color=Highlight&gt;Phoebe&lt;/color&gt; có thể dùng Mid-air Heavy Attack không giới hạn lần.
-STA tiêu hao khi bay giảm.
-Buff chính: &lt;color=Highlight&gt;Dùng Intro Skill&lt;/color&gt; cũng sẽ gây Aero Erosion và Spectro Frazzle lên mục tiêu.</t>
+&lt;color=Highlight&gt;Phoebe&lt;/color&gt; có thể sử dụng Đòn Heavy Attack giữa không trung không giới hạn.
+Chi phí STA khi bay giảm.
+Tăng cường chính: &lt;color=Highlight&gt;Kích hoạt Kỹ Năng giới thiệu&lt;/color&gt; cũng sẽ gây Aero Erosion và Spectro Frazzle lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -33380,9 +33399,9 @@
       <c r="M500" t="inlineStr">
         <is>
           <t>Trong thử thách này:
-&lt;color=Highlight&gt;Changli&lt;/color&gt; duy trì trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;.
-Chi phí STA khi bay được giảm.
-Buff chính: &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; triệu hồi Thiên Thạch khi trúng đích, gây Fusion DMG.</t>
+&lt;color=Highlight&gt;Changli&lt;/color&gt; duy trì trạng thái &lt;color=Highlight&gt;Thị Giác Chân Thực&lt;/color&gt;.
+Chi phí STA khi bay giảm.
+Tăng cường chính: &lt;color=Highlight&gt;Tấn Công giữa không trung&lt;/color&gt; sẽ triệu hồi Thiên Thạch khi trúng mục tiêu, gây DMG Fusion.</t>
         </is>
       </c>
     </row>
@@ -33452,8 +33471,8 @@
         <is>
           <t>Trong thử thách này:
 &lt;color=Highlight&gt;Yellow Light: Zoom&lt;/color&gt; của &lt;color=Highlight&gt;Lumi&lt;/color&gt; không tiêu hao STA.
-Chi phí STA khi bay được giảm.
-Buff chính: &lt;color=Highlight&gt;Đánh trúng mục tiêu bằng Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;gây DMG Basic Attack&lt;/color&gt; sẽ triệu hồi thêm Starfall gây Electro DMG.</t>
+Chi phí STA khi bay giảm.
+Tăng cường chính: &lt;color=Highlight&gt;Đánh trúng mục tiêu bằng Đòn Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;gây DMG Đòn Basic Attack&lt;/color&gt; sẽ bổ sung thêm Sao Băng gây DMG Electro.</t>
         </is>
       </c>
     </row>
